--- a/SoSerial.xlsx
+++ b/SoSerial.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\HK2Nam2\PTTKHTTT\DoAn\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A6E7A552-8F55-44C1-9E68-BEDAD40A08C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{513BB563-DFC9-4805-8A2C-7AFA23C2183E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AEEAB626-5BEE-420A-A42D-F78A94A6DE5E}"/>
   </bookViews>
@@ -1129,12 +1129,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="3">
@@ -1173,7 +1179,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
@@ -1186,6 +1192,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1574,7 +1583,7 @@
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="5" t="s">
         <v>1</v>
       </c>
       <c r="D2" s="1">
@@ -1586,7 +1595,7 @@
       <c r="G2" s="1">
         <v>1</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="5" t="s">
         <v>103</v>
       </c>
       <c r="J2" s="1">
@@ -1618,7 +1627,7 @@
       <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="5" t="s">
         <v>2</v>
       </c>
       <c r="D3" s="1">
@@ -1630,7 +1639,7 @@
       <c r="G3" s="1">
         <v>2</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="5" t="s">
         <v>104</v>
       </c>
       <c r="J3" s="1">
@@ -1662,7 +1671,7 @@
       <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="5" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="1">
@@ -1674,7 +1683,7 @@
       <c r="G4" s="1">
         <v>3</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="5" t="s">
         <v>105</v>
       </c>
       <c r="J4" s="1">
@@ -1706,7 +1715,7 @@
       <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D5" s="1">
@@ -1718,7 +1727,7 @@
       <c r="G5" s="1">
         <v>4</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H5" s="5" t="s">
         <v>106</v>
       </c>
       <c r="J5" s="1">
@@ -1750,7 +1759,7 @@
       <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="5" t="s">
         <v>5</v>
       </c>
       <c r="D6" s="1">
@@ -1762,7 +1771,7 @@
       <c r="G6" s="1">
         <v>5</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="H6" s="5" t="s">
         <v>107</v>
       </c>
       <c r="J6" s="1">
@@ -1794,7 +1803,7 @@
       <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="5" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="1">
@@ -1806,7 +1815,7 @@
       <c r="G7" s="1">
         <v>6</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="H7" s="5" t="s">
         <v>108</v>
       </c>
       <c r="J7" s="1">
@@ -1838,7 +1847,7 @@
       <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="5" t="s">
         <v>7</v>
       </c>
       <c r="D8" s="1">
@@ -1850,7 +1859,7 @@
       <c r="G8" s="1">
         <v>7</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="H8" s="5" t="s">
         <v>109</v>
       </c>
       <c r="J8" s="1">
@@ -1882,7 +1891,7 @@
       <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D9" s="1">
@@ -1894,7 +1903,7 @@
       <c r="G9" s="1">
         <v>8</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="H9" s="5" t="s">
         <v>110</v>
       </c>
       <c r="J9" s="1">
@@ -1926,7 +1935,7 @@
       <c r="A10" s="1">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D10" s="1">
@@ -1938,7 +1947,7 @@
       <c r="G10" s="1">
         <v>9</v>
       </c>
-      <c r="H10" s="2" t="s">
+      <c r="H10" s="5" t="s">
         <v>111</v>
       </c>
       <c r="J10" s="1">
@@ -1970,7 +1979,7 @@
       <c r="A11" s="1">
         <v>10</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="5" t="s">
         <v>10</v>
       </c>
       <c r="D11" s="1">
@@ -1982,7 +1991,7 @@
       <c r="G11" s="1">
         <v>10</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="H11" s="5" t="s">
         <v>112</v>
       </c>
       <c r="J11" s="1">

--- a/SoSerial.xlsx
+++ b/SoSerial.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\HK2Nam2\PTTKHTTT\DoAn\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{513BB563-DFC9-4805-8A2C-7AFA23C2183E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{119FF8DF-6129-4A60-B59F-44853C90F067}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AEEAB626-5BEE-420A-A42D-F78A94A6DE5E}"/>
   </bookViews>
@@ -1190,11 +1190,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1550,40 +1550,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="D1" s="4" t="s">
+      <c r="B1" s="5"/>
+      <c r="D1" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="E1" s="4"/>
-      <c r="G1" s="4" t="s">
+      <c r="E1" s="5"/>
+      <c r="G1" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="H1" s="4"/>
-      <c r="J1" s="4" t="s">
+      <c r="H1" s="5"/>
+      <c r="J1" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="K1" s="4"/>
-      <c r="M1" s="4" t="s">
+      <c r="K1" s="5"/>
+      <c r="M1" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="N1" s="4"/>
-      <c r="P1" s="4" t="s">
+      <c r="N1" s="5"/>
+      <c r="P1" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="Q1" s="4"/>
-      <c r="S1" s="4" t="s">
+      <c r="Q1" s="5"/>
+      <c r="S1" s="5" t="s">
         <v>306</v>
       </c>
-      <c r="T1" s="4"/>
+      <c r="T1" s="5"/>
     </row>
     <row r="2" spans="1:20" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="4" t="s">
         <v>1</v>
       </c>
       <c r="D2" s="1">
@@ -1595,7 +1595,7 @@
       <c r="G2" s="1">
         <v>1</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="4" t="s">
         <v>103</v>
       </c>
       <c r="J2" s="1">
@@ -1627,7 +1627,7 @@
       <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>2</v>
       </c>
       <c r="D3" s="1">
@@ -1639,7 +1639,7 @@
       <c r="G3" s="1">
         <v>2</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="4" t="s">
         <v>104</v>
       </c>
       <c r="J3" s="1">
@@ -1671,7 +1671,7 @@
       <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="1">
@@ -1683,7 +1683,7 @@
       <c r="G4" s="1">
         <v>3</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="4" t="s">
         <v>105</v>
       </c>
       <c r="J4" s="1">
@@ -1715,7 +1715,7 @@
       <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="4" t="s">
         <v>4</v>
       </c>
       <c r="D5" s="1">
@@ -1727,7 +1727,7 @@
       <c r="G5" s="1">
         <v>4</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="H5" s="4" t="s">
         <v>106</v>
       </c>
       <c r="J5" s="1">
@@ -1759,7 +1759,7 @@
       <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D6" s="1">
@@ -1771,7 +1771,7 @@
       <c r="G6" s="1">
         <v>5</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="H6" s="4" t="s">
         <v>107</v>
       </c>
       <c r="J6" s="1">
@@ -1803,7 +1803,7 @@
       <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D7" s="1">
@@ -1815,7 +1815,7 @@
       <c r="G7" s="1">
         <v>6</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="H7" s="4" t="s">
         <v>108</v>
       </c>
       <c r="J7" s="1">
@@ -1847,7 +1847,7 @@
       <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D8" s="1">
@@ -1859,7 +1859,7 @@
       <c r="G8" s="1">
         <v>7</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="H8" s="4" t="s">
         <v>109</v>
       </c>
       <c r="J8" s="1">
@@ -1891,7 +1891,7 @@
       <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D9" s="1">
@@ -1903,7 +1903,7 @@
       <c r="G9" s="1">
         <v>8</v>
       </c>
-      <c r="H9" s="5" t="s">
+      <c r="H9" s="4" t="s">
         <v>110</v>
       </c>
       <c r="J9" s="1">
@@ -1935,7 +1935,7 @@
       <c r="A10" s="1">
         <v>9</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D10" s="1">
@@ -1947,7 +1947,7 @@
       <c r="G10" s="1">
         <v>9</v>
       </c>
-      <c r="H10" s="5" t="s">
+      <c r="H10" s="4" t="s">
         <v>111</v>
       </c>
       <c r="J10" s="1">
@@ -1979,7 +1979,7 @@
       <c r="A11" s="1">
         <v>10</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D11" s="1">
@@ -1991,7 +1991,7 @@
       <c r="G11" s="1">
         <v>10</v>
       </c>
-      <c r="H11" s="5" t="s">
+      <c r="H11" s="4" t="s">
         <v>112</v>
       </c>
       <c r="J11" s="1">
@@ -3806,13 +3806,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="S1:T1"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="M1:N1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="S1:T1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SoSerial.xlsx
+++ b/SoSerial.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\HK2Nam2\PTTKHTTT\DoAn\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{119FF8DF-6129-4A60-B59F-44853C90F067}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5CDB7E2-4FD6-4B91-A2BF-727444F0DAF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AEEAB626-5BEE-420A-A42D-F78A94A6DE5E}"/>
   </bookViews>
@@ -1589,7 +1589,7 @@
       <c r="D2" s="1">
         <v>1</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="4" t="s">
         <v>51</v>
       </c>
       <c r="G2" s="1">
@@ -1601,19 +1601,19 @@
       <c r="J2" s="1">
         <v>1</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="4" t="s">
         <v>154</v>
       </c>
       <c r="M2" s="1">
         <v>1</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="N2" s="4" t="s">
         <v>205</v>
       </c>
       <c r="P2" s="1">
         <v>1</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="Q2" s="4" t="s">
         <v>256</v>
       </c>
       <c r="S2" s="1">
@@ -1633,7 +1633,7 @@
       <c r="D3" s="1">
         <v>2</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="4" t="s">
         <v>53</v>
       </c>
       <c r="G3" s="1">
@@ -1645,19 +1645,19 @@
       <c r="J3" s="1">
         <v>2</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" s="4" t="s">
         <v>155</v>
       </c>
       <c r="M3" s="1">
         <v>2</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="N3" s="4" t="s">
         <v>206</v>
       </c>
       <c r="P3" s="1">
         <v>2</v>
       </c>
-      <c r="Q3" s="2" t="s">
+      <c r="Q3" s="4" t="s">
         <v>257</v>
       </c>
       <c r="S3" s="1">
@@ -1677,7 +1677,7 @@
       <c r="D4" s="1">
         <v>3</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="4" t="s">
         <v>55</v>
       </c>
       <c r="G4" s="1">
@@ -1689,19 +1689,19 @@
       <c r="J4" s="1">
         <v>3</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="K4" s="4" t="s">
         <v>156</v>
       </c>
       <c r="M4" s="1">
         <v>3</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="N4" s="4" t="s">
         <v>207</v>
       </c>
       <c r="P4" s="1">
         <v>3</v>
       </c>
-      <c r="Q4" s="2" t="s">
+      <c r="Q4" s="4" t="s">
         <v>258</v>
       </c>
       <c r="S4" s="1">
@@ -1721,7 +1721,7 @@
       <c r="D5" s="1">
         <v>4</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="4" t="s">
         <v>57</v>
       </c>
       <c r="G5" s="1">
@@ -1733,19 +1733,19 @@
       <c r="J5" s="1">
         <v>4</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="K5" s="4" t="s">
         <v>157</v>
       </c>
       <c r="M5" s="1">
         <v>4</v>
       </c>
-      <c r="N5" s="2" t="s">
+      <c r="N5" s="4" t="s">
         <v>208</v>
       </c>
       <c r="P5" s="1">
         <v>4</v>
       </c>
-      <c r="Q5" s="2" t="s">
+      <c r="Q5" s="4" t="s">
         <v>259</v>
       </c>
       <c r="S5" s="1">
@@ -1765,7 +1765,7 @@
       <c r="D6" s="1">
         <v>5</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="4" t="s">
         <v>59</v>
       </c>
       <c r="G6" s="1">
@@ -1777,19 +1777,19 @@
       <c r="J6" s="1">
         <v>5</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="K6" s="4" t="s">
         <v>158</v>
       </c>
       <c r="M6" s="1">
         <v>5</v>
       </c>
-      <c r="N6" s="2" t="s">
+      <c r="N6" s="4" t="s">
         <v>209</v>
       </c>
       <c r="P6" s="1">
         <v>5</v>
       </c>
-      <c r="Q6" s="2" t="s">
+      <c r="Q6" s="4" t="s">
         <v>260</v>
       </c>
       <c r="S6" s="1">
@@ -1809,7 +1809,7 @@
       <c r="D7" s="1">
         <v>6</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="4" t="s">
         <v>61</v>
       </c>
       <c r="G7" s="1">
@@ -1821,19 +1821,19 @@
       <c r="J7" s="1">
         <v>6</v>
       </c>
-      <c r="K7" s="2" t="s">
+      <c r="K7" s="4" t="s">
         <v>159</v>
       </c>
       <c r="M7" s="1">
         <v>6</v>
       </c>
-      <c r="N7" s="2" t="s">
+      <c r="N7" s="4" t="s">
         <v>210</v>
       </c>
       <c r="P7" s="1">
         <v>6</v>
       </c>
-      <c r="Q7" s="2" t="s">
+      <c r="Q7" s="4" t="s">
         <v>261</v>
       </c>
       <c r="S7" s="1">
@@ -1853,7 +1853,7 @@
       <c r="D8" s="1">
         <v>7</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="4" t="s">
         <v>63</v>
       </c>
       <c r="G8" s="1">
@@ -1865,19 +1865,19 @@
       <c r="J8" s="1">
         <v>7</v>
       </c>
-      <c r="K8" s="2" t="s">
+      <c r="K8" s="4" t="s">
         <v>160</v>
       </c>
       <c r="M8" s="1">
         <v>7</v>
       </c>
-      <c r="N8" s="2" t="s">
+      <c r="N8" s="4" t="s">
         <v>211</v>
       </c>
       <c r="P8" s="1">
         <v>7</v>
       </c>
-      <c r="Q8" s="2" t="s">
+      <c r="Q8" s="4" t="s">
         <v>262</v>
       </c>
       <c r="S8" s="1">
@@ -1897,7 +1897,7 @@
       <c r="D9" s="1">
         <v>8</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="4" t="s">
         <v>65</v>
       </c>
       <c r="G9" s="1">
@@ -1909,19 +1909,19 @@
       <c r="J9" s="1">
         <v>8</v>
       </c>
-      <c r="K9" s="2" t="s">
+      <c r="K9" s="4" t="s">
         <v>161</v>
       </c>
       <c r="M9" s="1">
         <v>8</v>
       </c>
-      <c r="N9" s="2" t="s">
+      <c r="N9" s="4" t="s">
         <v>212</v>
       </c>
       <c r="P9" s="1">
         <v>8</v>
       </c>
-      <c r="Q9" s="2" t="s">
+      <c r="Q9" s="4" t="s">
         <v>263</v>
       </c>
       <c r="S9" s="1">
@@ -1941,7 +1941,7 @@
       <c r="D10" s="1">
         <v>9</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="4" t="s">
         <v>67</v>
       </c>
       <c r="G10" s="1">
@@ -1953,19 +1953,19 @@
       <c r="J10" s="1">
         <v>9</v>
       </c>
-      <c r="K10" s="2" t="s">
+      <c r="K10" s="4" t="s">
         <v>162</v>
       </c>
       <c r="M10" s="1">
         <v>9</v>
       </c>
-      <c r="N10" s="2" t="s">
+      <c r="N10" s="4" t="s">
         <v>213</v>
       </c>
       <c r="P10" s="1">
         <v>9</v>
       </c>
-      <c r="Q10" s="2" t="s">
+      <c r="Q10" s="4" t="s">
         <v>264</v>
       </c>
       <c r="S10" s="1">
@@ -1985,7 +1985,7 @@
       <c r="D11" s="1">
         <v>10</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="4" t="s">
         <v>69</v>
       </c>
       <c r="G11" s="1">
@@ -1997,19 +1997,19 @@
       <c r="J11" s="1">
         <v>10</v>
       </c>
-      <c r="K11" s="2" t="s">
+      <c r="K11" s="4" t="s">
         <v>163</v>
       </c>
       <c r="M11" s="1">
         <v>10</v>
       </c>
-      <c r="N11" s="2" t="s">
+      <c r="N11" s="4" t="s">
         <v>214</v>
       </c>
       <c r="P11" s="1">
         <v>10</v>
       </c>
-      <c r="Q11" s="2" t="s">
+      <c r="Q11" s="4" t="s">
         <v>265</v>
       </c>
       <c r="S11" s="1">
@@ -2023,7 +2023,7 @@
       <c r="A12" s="1">
         <v>11</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D12" s="1">
@@ -2035,13 +2035,13 @@
       <c r="G12" s="1">
         <v>11</v>
       </c>
-      <c r="H12" s="2" t="s">
+      <c r="H12" s="4" t="s">
         <v>113</v>
       </c>
       <c r="J12" s="1">
         <v>11</v>
       </c>
-      <c r="K12" s="2" t="s">
+      <c r="K12" s="4" t="s">
         <v>164</v>
       </c>
       <c r="M12" s="1">
@@ -2067,7 +2067,7 @@
       <c r="A13" s="1">
         <v>12</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D13" s="1">
@@ -2079,13 +2079,13 @@
       <c r="G13" s="1">
         <v>12</v>
       </c>
-      <c r="H13" s="2" t="s">
+      <c r="H13" s="4" t="s">
         <v>114</v>
       </c>
       <c r="J13" s="1">
         <v>12</v>
       </c>
-      <c r="K13" s="2" t="s">
+      <c r="K13" s="4" t="s">
         <v>165</v>
       </c>
       <c r="M13" s="1">
@@ -2111,7 +2111,7 @@
       <c r="A14" s="1">
         <v>13</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D14" s="1">
@@ -2123,13 +2123,13 @@
       <c r="G14" s="1">
         <v>13</v>
       </c>
-      <c r="H14" s="2" t="s">
+      <c r="H14" s="4" t="s">
         <v>115</v>
       </c>
       <c r="J14" s="1">
         <v>13</v>
       </c>
-      <c r="K14" s="2" t="s">
+      <c r="K14" s="4" t="s">
         <v>166</v>
       </c>
       <c r="M14" s="1">
@@ -2155,7 +2155,7 @@
       <c r="A15" s="1">
         <v>14</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D15" s="1">
@@ -2167,13 +2167,13 @@
       <c r="G15" s="1">
         <v>14</v>
       </c>
-      <c r="H15" s="2" t="s">
+      <c r="H15" s="4" t="s">
         <v>116</v>
       </c>
       <c r="J15" s="1">
         <v>14</v>
       </c>
-      <c r="K15" s="2" t="s">
+      <c r="K15" s="4" t="s">
         <v>167</v>
       </c>
       <c r="M15" s="1">
@@ -2199,7 +2199,7 @@
       <c r="A16" s="1">
         <v>15</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="4" t="s">
         <v>15</v>
       </c>
       <c r="D16" s="1">
@@ -2211,13 +2211,13 @@
       <c r="G16" s="1">
         <v>15</v>
       </c>
-      <c r="H16" s="2" t="s">
+      <c r="H16" s="4" t="s">
         <v>117</v>
       </c>
       <c r="J16" s="1">
         <v>15</v>
       </c>
-      <c r="K16" s="2" t="s">
+      <c r="K16" s="4" t="s">
         <v>168</v>
       </c>
       <c r="M16" s="1">
@@ -2255,13 +2255,13 @@
       <c r="G17" s="1">
         <v>16</v>
       </c>
-      <c r="H17" s="2" t="s">
+      <c r="H17" s="4" t="s">
         <v>118</v>
       </c>
       <c r="J17" s="1">
         <v>16</v>
       </c>
-      <c r="K17" s="2" t="s">
+      <c r="K17" s="4" t="s">
         <v>169</v>
       </c>
       <c r="M17" s="1">
@@ -2299,13 +2299,13 @@
       <c r="G18" s="1">
         <v>17</v>
       </c>
-      <c r="H18" s="2" t="s">
+      <c r="H18" s="4" t="s">
         <v>119</v>
       </c>
       <c r="J18" s="1">
         <v>17</v>
       </c>
-      <c r="K18" s="2" t="s">
+      <c r="K18" s="4" t="s">
         <v>170</v>
       </c>
       <c r="M18" s="1">
@@ -2343,13 +2343,13 @@
       <c r="G19" s="1">
         <v>18</v>
       </c>
-      <c r="H19" s="2" t="s">
+      <c r="H19" s="4" t="s">
         <v>120</v>
       </c>
       <c r="J19" s="1">
         <v>18</v>
       </c>
-      <c r="K19" s="2" t="s">
+      <c r="K19" s="4" t="s">
         <v>171</v>
       </c>
       <c r="M19" s="1">
@@ -2387,13 +2387,13 @@
       <c r="G20" s="1">
         <v>19</v>
       </c>
-      <c r="H20" s="2" t="s">
+      <c r="H20" s="4" t="s">
         <v>121</v>
       </c>
       <c r="J20" s="1">
         <v>19</v>
       </c>
-      <c r="K20" s="2" t="s">
+      <c r="K20" s="4" t="s">
         <v>172</v>
       </c>
       <c r="M20" s="1">
@@ -2431,13 +2431,13 @@
       <c r="G21" s="1">
         <v>20</v>
       </c>
-      <c r="H21" s="2" t="s">
+      <c r="H21" s="4" t="s">
         <v>122</v>
       </c>
       <c r="J21" s="1">
         <v>20</v>
       </c>
-      <c r="K21" s="2" t="s">
+      <c r="K21" s="4" t="s">
         <v>173</v>
       </c>
       <c r="M21" s="1">

--- a/SoSerial.xlsx
+++ b/SoSerial.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\HK2Nam2\PTTKHTTT\DoAn\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5CDB7E2-4FD6-4B91-A2BF-727444F0DAF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01AB45D3-6F19-4689-8594-4753FAEFF472}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AEEAB626-5BEE-420A-A42D-F78A94A6DE5E}"/>
   </bookViews>
@@ -1179,7 +1179,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
@@ -1195,6 +1195,19 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1554,30 +1567,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="5"/>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="E1" s="5"/>
-      <c r="G1" s="5" t="s">
+      <c r="E1" s="7"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="H1" s="5"/>
-      <c r="J1" s="5" t="s">
+      <c r="H1" s="7"/>
+      <c r="J1" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="K1" s="5"/>
-      <c r="M1" s="5" t="s">
+      <c r="K1" s="7"/>
+      <c r="M1" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="N1" s="5"/>
-      <c r="P1" s="5" t="s">
+      <c r="N1" s="7"/>
+      <c r="P1" s="7" t="s">
         <v>255</v>
       </c>
-      <c r="Q1" s="5"/>
-      <c r="S1" s="5" t="s">
+      <c r="Q1" s="7"/>
+      <c r="S1" s="7" t="s">
         <v>306</v>
       </c>
-      <c r="T1" s="5"/>
+      <c r="T1" s="7"/>
     </row>
     <row r="2" spans="1:20" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
@@ -1586,40 +1600,41 @@
       <c r="B2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2" s="9">
         <v>1</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="G2" s="1">
+      <c r="F2" s="8"/>
+      <c r="G2" s="9">
         <v>1</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="J2" s="1">
+      <c r="J2" s="9">
         <v>1</v>
       </c>
       <c r="K2" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="M2" s="1">
+      <c r="M2" s="9">
         <v>1</v>
       </c>
       <c r="N2" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="P2" s="1">
+      <c r="P2" s="9">
         <v>1</v>
       </c>
       <c r="Q2" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="S2" s="1">
+      <c r="S2" s="9">
         <v>1</v>
       </c>
-      <c r="T2" s="2" t="s">
+      <c r="T2" s="4" t="s">
         <v>307</v>
       </c>
     </row>
@@ -1630,40 +1645,41 @@
       <c r="B3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3" s="9">
         <v>2</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="G3" s="1">
+      <c r="F3" s="8"/>
+      <c r="G3" s="9">
         <v>2</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="J3" s="1">
+      <c r="J3" s="9">
         <v>2</v>
       </c>
       <c r="K3" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="M3" s="1">
+      <c r="M3" s="9">
         <v>2</v>
       </c>
       <c r="N3" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="P3" s="1">
+      <c r="P3" s="9">
         <v>2</v>
       </c>
       <c r="Q3" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="S3" s="1">
+      <c r="S3" s="9">
         <v>2</v>
       </c>
-      <c r="T3" s="2" t="s">
+      <c r="T3" s="4" t="s">
         <v>308</v>
       </c>
     </row>
@@ -1674,40 +1690,41 @@
       <c r="B4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" s="9">
         <v>3</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="G4" s="1">
+      <c r="F4" s="8"/>
+      <c r="G4" s="9">
         <v>3</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="J4" s="1">
+      <c r="J4" s="9">
         <v>3</v>
       </c>
       <c r="K4" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="M4" s="1">
+      <c r="M4" s="9">
         <v>3</v>
       </c>
       <c r="N4" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="P4" s="1">
+      <c r="P4" s="9">
         <v>3</v>
       </c>
       <c r="Q4" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="S4" s="1">
+      <c r="S4" s="9">
         <v>3</v>
       </c>
-      <c r="T4" s="2" t="s">
+      <c r="T4" s="4" t="s">
         <v>309</v>
       </c>
     </row>
@@ -1718,40 +1735,41 @@
       <c r="B5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5" s="9">
         <v>4</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="G5" s="1">
+      <c r="F5" s="8"/>
+      <c r="G5" s="9">
         <v>4</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="J5" s="1">
+      <c r="J5" s="9">
         <v>4</v>
       </c>
       <c r="K5" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="M5" s="1">
+      <c r="M5" s="9">
         <v>4</v>
       </c>
       <c r="N5" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="P5" s="1">
+      <c r="P5" s="9">
         <v>4</v>
       </c>
       <c r="Q5" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="S5" s="1">
+      <c r="S5" s="9">
         <v>4</v>
       </c>
-      <c r="T5" s="2" t="s">
+      <c r="T5" s="4" t="s">
         <v>310</v>
       </c>
     </row>
@@ -1762,40 +1780,41 @@
       <c r="B6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6" s="9">
         <v>5</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="G6" s="1">
+      <c r="F6" s="8"/>
+      <c r="G6" s="9">
         <v>5</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="J6" s="1">
+      <c r="J6" s="9">
         <v>5</v>
       </c>
       <c r="K6" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="M6" s="1">
+      <c r="M6" s="9">
         <v>5</v>
       </c>
       <c r="N6" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="P6" s="1">
+      <c r="P6" s="9">
         <v>5</v>
       </c>
       <c r="Q6" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="S6" s="1">
+      <c r="S6" s="9">
         <v>5</v>
       </c>
-      <c r="T6" s="2" t="s">
+      <c r="T6" s="4" t="s">
         <v>311</v>
       </c>
     </row>
@@ -1806,40 +1825,41 @@
       <c r="B7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D7" s="9">
         <v>6</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="G7" s="1">
+      <c r="F7" s="8"/>
+      <c r="G7" s="9">
         <v>6</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="J7" s="1">
+      <c r="J7" s="9">
         <v>6</v>
       </c>
       <c r="K7" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="M7" s="1">
+      <c r="M7" s="9">
         <v>6</v>
       </c>
       <c r="N7" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="P7" s="1">
+      <c r="P7" s="9">
         <v>6</v>
       </c>
       <c r="Q7" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="S7" s="1">
+      <c r="S7" s="9">
         <v>6</v>
       </c>
-      <c r="T7" s="2" t="s">
+      <c r="T7" s="6" t="s">
         <v>312</v>
       </c>
     </row>
@@ -1850,40 +1870,41 @@
       <c r="B8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D8" s="9">
         <v>7</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="G8" s="1">
+      <c r="F8" s="8"/>
+      <c r="G8" s="9">
         <v>7</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="J8" s="1">
+      <c r="J8" s="9">
         <v>7</v>
       </c>
       <c r="K8" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="M8" s="1">
+      <c r="M8" s="9">
         <v>7</v>
       </c>
       <c r="N8" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="P8" s="1">
+      <c r="P8" s="9">
         <v>7</v>
       </c>
       <c r="Q8" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="S8" s="1">
+      <c r="S8" s="9">
         <v>7</v>
       </c>
-      <c r="T8" s="2" t="s">
+      <c r="T8" s="6" t="s">
         <v>313</v>
       </c>
     </row>
@@ -1894,40 +1915,41 @@
       <c r="B9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D9" s="9">
         <v>8</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="G9" s="1">
+      <c r="F9" s="8"/>
+      <c r="G9" s="9">
         <v>8</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="J9" s="1">
+      <c r="J9" s="9">
         <v>8</v>
       </c>
       <c r="K9" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="M9" s="1">
+      <c r="M9" s="9">
         <v>8</v>
       </c>
       <c r="N9" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="P9" s="1">
+      <c r="P9" s="9">
         <v>8</v>
       </c>
       <c r="Q9" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="S9" s="1">
+      <c r="S9" s="9">
         <v>8</v>
       </c>
-      <c r="T9" s="2" t="s">
+      <c r="T9" s="6" t="s">
         <v>314</v>
       </c>
     </row>
@@ -1938,40 +1960,41 @@
       <c r="B10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D10" s="9">
         <v>9</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="G10" s="1">
+      <c r="F10" s="8"/>
+      <c r="G10" s="9">
         <v>9</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="J10" s="1">
+      <c r="J10" s="9">
         <v>9</v>
       </c>
       <c r="K10" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="M10" s="1">
+      <c r="M10" s="9">
         <v>9</v>
       </c>
       <c r="N10" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="P10" s="1">
+      <c r="P10" s="9">
         <v>9</v>
       </c>
       <c r="Q10" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="S10" s="1">
+      <c r="S10" s="9">
         <v>9</v>
       </c>
-      <c r="T10" s="2" t="s">
+      <c r="T10" s="6" t="s">
         <v>315</v>
       </c>
     </row>
@@ -1982,40 +2005,41 @@
       <c r="B11" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="1">
+      <c r="D11" s="9">
         <v>10</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="G11" s="1">
+      <c r="F11" s="8"/>
+      <c r="G11" s="9">
         <v>10</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="J11" s="1">
+      <c r="J11" s="9">
         <v>10</v>
       </c>
       <c r="K11" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="M11" s="1">
+      <c r="M11" s="9">
         <v>10</v>
       </c>
       <c r="N11" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="P11" s="1">
+      <c r="P11" s="9">
         <v>10</v>
       </c>
       <c r="Q11" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="S11" s="1">
+      <c r="S11" s="9">
         <v>10</v>
       </c>
-      <c r="T11" s="2" t="s">
+      <c r="T11" s="6" t="s">
         <v>316</v>
       </c>
     </row>
@@ -2026,40 +2050,41 @@
       <c r="B12" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="1">
+      <c r="D12" s="9">
         <v>11</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="G12" s="1">
+      <c r="F12" s="8"/>
+      <c r="G12" s="9">
         <v>11</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="J12" s="1">
+      <c r="J12" s="9">
         <v>11</v>
       </c>
       <c r="K12" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="M12" s="1">
+      <c r="M12" s="9">
         <v>11</v>
       </c>
-      <c r="N12" s="2" t="s">
+      <c r="N12" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="P12" s="1">
+      <c r="P12" s="9">
         <v>11</v>
       </c>
-      <c r="Q12" s="2" t="s">
+      <c r="Q12" s="6" t="s">
         <v>266</v>
       </c>
-      <c r="S12" s="1">
+      <c r="S12" s="9">
         <v>11</v>
       </c>
-      <c r="T12" s="2" t="s">
+      <c r="T12" s="6" t="s">
         <v>317</v>
       </c>
     </row>
@@ -2070,40 +2095,41 @@
       <c r="B13" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="1">
+      <c r="D13" s="9">
         <v>12</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="G13" s="1">
+      <c r="F13" s="8"/>
+      <c r="G13" s="9">
         <v>12</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="J13" s="1">
+      <c r="J13" s="9">
         <v>12</v>
       </c>
       <c r="K13" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="M13" s="1">
+      <c r="M13" s="9">
         <v>12</v>
       </c>
-      <c r="N13" s="2" t="s">
+      <c r="N13" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="P13" s="1">
+      <c r="P13" s="9">
         <v>12</v>
       </c>
-      <c r="Q13" s="2" t="s">
+      <c r="Q13" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="S13" s="1">
+      <c r="S13" s="9">
         <v>12</v>
       </c>
-      <c r="T13" s="2" t="s">
+      <c r="T13" s="6" t="s">
         <v>318</v>
       </c>
     </row>
@@ -2114,40 +2140,41 @@
       <c r="B14" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D14" s="1">
+      <c r="D14" s="9">
         <v>13</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="G14" s="1">
+      <c r="F14" s="8"/>
+      <c r="G14" s="9">
         <v>13</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="J14" s="1">
+      <c r="J14" s="9">
         <v>13</v>
       </c>
       <c r="K14" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="M14" s="1">
+      <c r="M14" s="9">
         <v>13</v>
       </c>
-      <c r="N14" s="2" t="s">
+      <c r="N14" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="P14" s="1">
+      <c r="P14" s="9">
         <v>13</v>
       </c>
-      <c r="Q14" s="2" t="s">
+      <c r="Q14" s="6" t="s">
         <v>268</v>
       </c>
-      <c r="S14" s="1">
+      <c r="S14" s="9">
         <v>13</v>
       </c>
-      <c r="T14" s="2" t="s">
+      <c r="T14" s="6" t="s">
         <v>319</v>
       </c>
     </row>
@@ -2158,40 +2185,41 @@
       <c r="B15" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="1">
+      <c r="D15" s="9">
         <v>14</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E15" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="G15" s="1">
+      <c r="F15" s="8"/>
+      <c r="G15" s="9">
         <v>14</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="J15" s="1">
+      <c r="J15" s="9">
         <v>14</v>
       </c>
-      <c r="K15" s="4" t="s">
+      <c r="K15" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="M15" s="1">
+      <c r="M15" s="9">
         <v>14</v>
       </c>
-      <c r="N15" s="2" t="s">
+      <c r="N15" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="P15" s="1">
+      <c r="P15" s="9">
         <v>14</v>
       </c>
-      <c r="Q15" s="2" t="s">
+      <c r="Q15" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="S15" s="1">
+      <c r="S15" s="9">
         <v>14</v>
       </c>
-      <c r="T15" s="2" t="s">
+      <c r="T15" s="6" t="s">
         <v>320</v>
       </c>
     </row>
@@ -2202,40 +2230,41 @@
       <c r="B16" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D16" s="1">
+      <c r="D16" s="9">
         <v>15</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E16" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="G16" s="1">
+      <c r="F16" s="8"/>
+      <c r="G16" s="9">
         <v>15</v>
       </c>
       <c r="H16" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="J16" s="1">
+      <c r="J16" s="9">
         <v>15</v>
       </c>
-      <c r="K16" s="4" t="s">
+      <c r="K16" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="M16" s="1">
+      <c r="M16" s="9">
         <v>15</v>
       </c>
-      <c r="N16" s="2" t="s">
+      <c r="N16" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="P16" s="1">
+      <c r="P16" s="9">
         <v>15</v>
       </c>
-      <c r="Q16" s="2" t="s">
+      <c r="Q16" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="S16" s="1">
+      <c r="S16" s="9">
         <v>15</v>
       </c>
-      <c r="T16" s="2" t="s">
+      <c r="T16" s="6" t="s">
         <v>321</v>
       </c>
     </row>
@@ -2243,43 +2272,44 @@
       <c r="A17" s="1">
         <v>16</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D17" s="1">
+      <c r="D17" s="9">
         <v>16</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E17" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="G17" s="1">
+      <c r="F17" s="8"/>
+      <c r="G17" s="9">
         <v>16</v>
       </c>
       <c r="H17" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="J17" s="1">
+      <c r="J17" s="9">
         <v>16</v>
       </c>
-      <c r="K17" s="4" t="s">
+      <c r="K17" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="M17" s="1">
+      <c r="M17" s="9">
         <v>16</v>
       </c>
-      <c r="N17" s="2" t="s">
+      <c r="N17" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="P17" s="1">
+      <c r="P17" s="9">
         <v>16</v>
       </c>
-      <c r="Q17" s="2" t="s">
+      <c r="Q17" s="6" t="s">
         <v>271</v>
       </c>
-      <c r="S17" s="1">
+      <c r="S17" s="9">
         <v>16</v>
       </c>
-      <c r="T17" s="2" t="s">
+      <c r="T17" s="6" t="s">
         <v>322</v>
       </c>
     </row>
@@ -2287,43 +2317,44 @@
       <c r="A18" s="1">
         <v>17</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D18" s="1">
+      <c r="D18" s="9">
         <v>17</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="E18" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="G18" s="1">
+      <c r="F18" s="8"/>
+      <c r="G18" s="9">
         <v>17</v>
       </c>
       <c r="H18" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="J18" s="1">
+      <c r="J18" s="9">
         <v>17</v>
       </c>
-      <c r="K18" s="4" t="s">
+      <c r="K18" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="M18" s="1">
+      <c r="M18" s="9">
         <v>17</v>
       </c>
-      <c r="N18" s="2" t="s">
+      <c r="N18" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="P18" s="1">
+      <c r="P18" s="9">
         <v>17</v>
       </c>
-      <c r="Q18" s="2" t="s">
+      <c r="Q18" s="6" t="s">
         <v>272</v>
       </c>
-      <c r="S18" s="1">
+      <c r="S18" s="9">
         <v>17</v>
       </c>
-      <c r="T18" s="2" t="s">
+      <c r="T18" s="6" t="s">
         <v>323</v>
       </c>
     </row>
@@ -2331,43 +2362,44 @@
       <c r="A19" s="1">
         <v>18</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D19" s="1">
+      <c r="D19" s="9">
         <v>18</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E19" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="G19" s="1">
+      <c r="F19" s="8"/>
+      <c r="G19" s="9">
         <v>18</v>
       </c>
       <c r="H19" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="J19" s="1">
+      <c r="J19" s="9">
         <v>18</v>
       </c>
-      <c r="K19" s="4" t="s">
+      <c r="K19" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="M19" s="1">
+      <c r="M19" s="9">
         <v>18</v>
       </c>
-      <c r="N19" s="2" t="s">
+      <c r="N19" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="P19" s="1">
+      <c r="P19" s="9">
         <v>18</v>
       </c>
-      <c r="Q19" s="2" t="s">
+      <c r="Q19" s="6" t="s">
         <v>273</v>
       </c>
-      <c r="S19" s="1">
+      <c r="S19" s="9">
         <v>18</v>
       </c>
-      <c r="T19" s="2" t="s">
+      <c r="T19" s="6" t="s">
         <v>324</v>
       </c>
     </row>
@@ -2375,43 +2407,44 @@
       <c r="A20" s="1">
         <v>19</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D20" s="1">
+      <c r="D20" s="9">
         <v>19</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="E20" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="G20" s="1">
+      <c r="F20" s="8"/>
+      <c r="G20" s="9">
         <v>19</v>
       </c>
-      <c r="H20" s="4" t="s">
+      <c r="H20" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="J20" s="1">
+      <c r="J20" s="9">
         <v>19</v>
       </c>
-      <c r="K20" s="4" t="s">
+      <c r="K20" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="M20" s="1">
+      <c r="M20" s="9">
         <v>19</v>
       </c>
-      <c r="N20" s="2" t="s">
+      <c r="N20" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="P20" s="1">
+      <c r="P20" s="9">
         <v>19</v>
       </c>
-      <c r="Q20" s="2" t="s">
+      <c r="Q20" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="S20" s="1">
+      <c r="S20" s="9">
         <v>19</v>
       </c>
-      <c r="T20" s="2" t="s">
+      <c r="T20" s="6" t="s">
         <v>325</v>
       </c>
     </row>
@@ -2419,43 +2452,44 @@
       <c r="A21" s="1">
         <v>20</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D21" s="1">
+      <c r="D21" s="9">
         <v>20</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="E21" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="G21" s="1">
+      <c r="F21" s="8"/>
+      <c r="G21" s="9">
         <v>20</v>
       </c>
-      <c r="H21" s="4" t="s">
+      <c r="H21" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="J21" s="1">
+      <c r="J21" s="9">
         <v>20</v>
       </c>
-      <c r="K21" s="4" t="s">
+      <c r="K21" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="M21" s="1">
+      <c r="M21" s="9">
         <v>20</v>
       </c>
-      <c r="N21" s="2" t="s">
+      <c r="N21" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="P21" s="1">
+      <c r="P21" s="9">
         <v>20</v>
       </c>
-      <c r="Q21" s="2" t="s">
+      <c r="Q21" s="6" t="s">
         <v>275</v>
       </c>
-      <c r="S21" s="1">
+      <c r="S21" s="9">
         <v>20</v>
       </c>
-      <c r="T21" s="2" t="s">
+      <c r="T21" s="6" t="s">
         <v>326</v>
       </c>
     </row>
@@ -2466,40 +2500,41 @@
       <c r="B22" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D22" s="1">
+      <c r="D22" s="9">
         <v>21</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="E22" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="G22" s="1">
+      <c r="F22" s="8"/>
+      <c r="G22" s="9">
         <v>21</v>
       </c>
-      <c r="H22" s="2" t="s">
+      <c r="H22" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="J22" s="1">
+      <c r="J22" s="9">
         <v>21</v>
       </c>
-      <c r="K22" s="2" t="s">
+      <c r="K22" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="M22" s="1">
+      <c r="M22" s="9">
         <v>21</v>
       </c>
-      <c r="N22" s="2" t="s">
+      <c r="N22" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="P22" s="1">
+      <c r="P22" s="9">
         <v>21</v>
       </c>
-      <c r="Q22" s="2" t="s">
+      <c r="Q22" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="S22" s="1">
+      <c r="S22" s="9">
         <v>21</v>
       </c>
-      <c r="T22" s="2" t="s">
+      <c r="T22" s="6" t="s">
         <v>327</v>
       </c>
     </row>
@@ -2510,40 +2545,41 @@
       <c r="B23" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D23" s="1">
+      <c r="D23" s="9">
         <v>22</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="E23" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="G23" s="1">
+      <c r="F23" s="8"/>
+      <c r="G23" s="9">
         <v>22</v>
       </c>
-      <c r="H23" s="2" t="s">
+      <c r="H23" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="J23" s="1">
+      <c r="J23" s="9">
         <v>22</v>
       </c>
-      <c r="K23" s="2" t="s">
+      <c r="K23" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="M23" s="1">
+      <c r="M23" s="9">
         <v>22</v>
       </c>
-      <c r="N23" s="2" t="s">
+      <c r="N23" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="P23" s="1">
+      <c r="P23" s="9">
         <v>22</v>
       </c>
-      <c r="Q23" s="2" t="s">
+      <c r="Q23" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="S23" s="1">
+      <c r="S23" s="9">
         <v>22</v>
       </c>
-      <c r="T23" s="2" t="s">
+      <c r="T23" s="6" t="s">
         <v>328</v>
       </c>
     </row>
@@ -2554,40 +2590,41 @@
       <c r="B24" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D24" s="1">
+      <c r="D24" s="9">
         <v>23</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="E24" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="G24" s="1">
+      <c r="F24" s="8"/>
+      <c r="G24" s="9">
         <v>23</v>
       </c>
-      <c r="H24" s="2" t="s">
+      <c r="H24" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="J24" s="1">
+      <c r="J24" s="9">
         <v>23</v>
       </c>
-      <c r="K24" s="2" t="s">
+      <c r="K24" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="M24" s="1">
+      <c r="M24" s="9">
         <v>23</v>
       </c>
-      <c r="N24" s="2" t="s">
+      <c r="N24" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="P24" s="1">
+      <c r="P24" s="9">
         <v>23</v>
       </c>
-      <c r="Q24" s="2" t="s">
+      <c r="Q24" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="S24" s="1">
+      <c r="S24" s="9">
         <v>23</v>
       </c>
-      <c r="T24" s="2" t="s">
+      <c r="T24" s="6" t="s">
         <v>329</v>
       </c>
     </row>
@@ -2598,40 +2635,41 @@
       <c r="B25" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D25" s="1">
+      <c r="D25" s="9">
         <v>24</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="E25" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="G25" s="1">
+      <c r="F25" s="8"/>
+      <c r="G25" s="9">
         <v>24</v>
       </c>
-      <c r="H25" s="2" t="s">
+      <c r="H25" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="J25" s="1">
+      <c r="J25" s="9">
         <v>24</v>
       </c>
-      <c r="K25" s="2" t="s">
+      <c r="K25" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="M25" s="1">
+      <c r="M25" s="9">
         <v>24</v>
       </c>
-      <c r="N25" s="2" t="s">
+      <c r="N25" s="6" t="s">
         <v>228</v>
       </c>
-      <c r="P25" s="1">
+      <c r="P25" s="9">
         <v>24</v>
       </c>
-      <c r="Q25" s="2" t="s">
+      <c r="Q25" s="6" t="s">
         <v>279</v>
       </c>
-      <c r="S25" s="1">
+      <c r="S25" s="9">
         <v>24</v>
       </c>
-      <c r="T25" s="2" t="s">
+      <c r="T25" s="6" t="s">
         <v>330</v>
       </c>
     </row>
@@ -2642,40 +2680,41 @@
       <c r="B26" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D26" s="1">
+      <c r="D26" s="9">
         <v>25</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="E26" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="G26" s="1">
+      <c r="F26" s="8"/>
+      <c r="G26" s="9">
         <v>25</v>
       </c>
-      <c r="H26" s="2" t="s">
+      <c r="H26" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="J26" s="1">
+      <c r="J26" s="9">
         <v>25</v>
       </c>
-      <c r="K26" s="2" t="s">
+      <c r="K26" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="M26" s="1">
+      <c r="M26" s="9">
         <v>25</v>
       </c>
-      <c r="N26" s="2" t="s">
+      <c r="N26" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="P26" s="1">
+      <c r="P26" s="9">
         <v>25</v>
       </c>
-      <c r="Q26" s="2" t="s">
+      <c r="Q26" s="6" t="s">
         <v>280</v>
       </c>
-      <c r="S26" s="1">
+      <c r="S26" s="9">
         <v>25</v>
       </c>
-      <c r="T26" s="2" t="s">
+      <c r="T26" s="6" t="s">
         <v>331</v>
       </c>
     </row>
@@ -2687,40 +2726,41 @@
         <v>26</v>
       </c>
       <c r="C27" s="2"/>
-      <c r="D27" s="1">
+      <c r="D27" s="9">
         <v>26</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="E27" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="G27" s="1">
+      <c r="F27" s="8"/>
+      <c r="G27" s="9">
         <v>26</v>
       </c>
-      <c r="H27" s="3" t="s">
+      <c r="H27" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="J27" s="1">
+      <c r="J27" s="9">
         <v>26</v>
       </c>
-      <c r="K27" s="2" t="s">
+      <c r="K27" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="M27" s="1">
+      <c r="M27" s="9">
         <v>26</v>
       </c>
-      <c r="N27" s="2" t="s">
+      <c r="N27" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="P27" s="1">
+      <c r="P27" s="9">
         <v>26</v>
       </c>
-      <c r="Q27" s="2" t="s">
+      <c r="Q27" s="6" t="s">
         <v>281</v>
       </c>
-      <c r="S27" s="1">
+      <c r="S27" s="9">
         <v>26</v>
       </c>
-      <c r="T27" s="3" t="s">
+      <c r="T27" s="10" t="s">
         <v>332</v>
       </c>
     </row>
@@ -2732,40 +2772,41 @@
         <v>27</v>
       </c>
       <c r="C28" s="2"/>
-      <c r="D28" s="1">
+      <c r="D28" s="9">
         <v>27</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="E28" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="G28" s="1">
+      <c r="F28" s="8"/>
+      <c r="G28" s="9">
         <v>27</v>
       </c>
-      <c r="H28" s="3" t="s">
+      <c r="H28" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="J28" s="1">
+      <c r="J28" s="9">
         <v>27</v>
       </c>
-      <c r="K28" s="2" t="s">
+      <c r="K28" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="M28" s="1">
+      <c r="M28" s="9">
         <v>27</v>
       </c>
-      <c r="N28" s="2" t="s">
+      <c r="N28" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="P28" s="1">
+      <c r="P28" s="9">
         <v>27</v>
       </c>
-      <c r="Q28" s="2" t="s">
+      <c r="Q28" s="6" t="s">
         <v>282</v>
       </c>
-      <c r="S28" s="1">
+      <c r="S28" s="9">
         <v>27</v>
       </c>
-      <c r="T28" s="3" t="s">
+      <c r="T28" s="10" t="s">
         <v>333</v>
       </c>
     </row>
@@ -2777,40 +2818,41 @@
         <v>28</v>
       </c>
       <c r="C29" s="2"/>
-      <c r="D29" s="1">
+      <c r="D29" s="9">
         <v>28</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="E29" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="G29" s="1">
+      <c r="F29" s="8"/>
+      <c r="G29" s="9">
         <v>28</v>
       </c>
-      <c r="H29" s="3" t="s">
+      <c r="H29" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="J29" s="1">
+      <c r="J29" s="9">
         <v>28</v>
       </c>
-      <c r="K29" s="2" t="s">
+      <c r="K29" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="M29" s="1">
+      <c r="M29" s="9">
         <v>28</v>
       </c>
-      <c r="N29" s="2" t="s">
+      <c r="N29" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="P29" s="1">
+      <c r="P29" s="9">
         <v>28</v>
       </c>
-      <c r="Q29" s="2" t="s">
+      <c r="Q29" s="6" t="s">
         <v>283</v>
       </c>
-      <c r="S29" s="1">
+      <c r="S29" s="9">
         <v>28</v>
       </c>
-      <c r="T29" s="3" t="s">
+      <c r="T29" s="10" t="s">
         <v>334</v>
       </c>
     </row>
@@ -2822,40 +2864,41 @@
         <v>29</v>
       </c>
       <c r="C30" s="2"/>
-      <c r="D30" s="1">
+      <c r="D30" s="9">
         <v>29</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="E30" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="G30" s="1">
+      <c r="F30" s="8"/>
+      <c r="G30" s="9">
         <v>29</v>
       </c>
-      <c r="H30" s="3" t="s">
+      <c r="H30" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="J30" s="1">
+      <c r="J30" s="9">
         <v>29</v>
       </c>
-      <c r="K30" s="2" t="s">
+      <c r="K30" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="M30" s="1">
+      <c r="M30" s="9">
         <v>29</v>
       </c>
-      <c r="N30" s="2" t="s">
+      <c r="N30" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="P30" s="1">
+      <c r="P30" s="9">
         <v>29</v>
       </c>
-      <c r="Q30" s="2" t="s">
+      <c r="Q30" s="6" t="s">
         <v>284</v>
       </c>
-      <c r="S30" s="1">
+      <c r="S30" s="9">
         <v>29</v>
       </c>
-      <c r="T30" s="3" t="s">
+      <c r="T30" s="10" t="s">
         <v>335</v>
       </c>
     </row>
@@ -2867,40 +2910,41 @@
         <v>30</v>
       </c>
       <c r="C31" s="2"/>
-      <c r="D31" s="1">
+      <c r="D31" s="9">
         <v>30</v>
       </c>
-      <c r="E31" s="2" t="s">
+      <c r="E31" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="G31" s="1">
+      <c r="F31" s="8"/>
+      <c r="G31" s="9">
         <v>30</v>
       </c>
-      <c r="H31" s="3" t="s">
+      <c r="H31" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="J31" s="1">
+      <c r="J31" s="9">
         <v>30</v>
       </c>
-      <c r="K31" s="2" t="s">
+      <c r="K31" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="M31" s="1">
+      <c r="M31" s="9">
         <v>30</v>
       </c>
-      <c r="N31" s="2" t="s">
+      <c r="N31" s="6" t="s">
         <v>234</v>
       </c>
-      <c r="P31" s="1">
+      <c r="P31" s="9">
         <v>30</v>
       </c>
-      <c r="Q31" s="2" t="s">
+      <c r="Q31" s="6" t="s">
         <v>285</v>
       </c>
-      <c r="S31" s="1">
+      <c r="S31" s="9">
         <v>30</v>
       </c>
-      <c r="T31" s="3" t="s">
+      <c r="T31" s="10" t="s">
         <v>336</v>
       </c>
     </row>
@@ -2912,40 +2956,41 @@
         <v>31</v>
       </c>
       <c r="C32" s="2"/>
-      <c r="D32" s="1">
+      <c r="D32" s="9">
         <v>31</v>
       </c>
-      <c r="E32" s="3" t="s">
+      <c r="E32" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="G32" s="1">
+      <c r="F32" s="8"/>
+      <c r="G32" s="9">
         <v>31</v>
       </c>
-      <c r="H32" s="3" t="s">
+      <c r="H32" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="J32" s="1">
+      <c r="J32" s="9">
         <v>31</v>
       </c>
-      <c r="K32" s="2" t="s">
+      <c r="K32" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="M32" s="1">
+      <c r="M32" s="9">
         <v>31</v>
       </c>
-      <c r="N32" s="2" t="s">
+      <c r="N32" s="6" t="s">
         <v>235</v>
       </c>
-      <c r="P32" s="1">
+      <c r="P32" s="9">
         <v>31</v>
       </c>
-      <c r="Q32" s="2" t="s">
+      <c r="Q32" s="6" t="s">
         <v>286</v>
       </c>
-      <c r="S32" s="1">
+      <c r="S32" s="9">
         <v>31</v>
       </c>
-      <c r="T32" s="3" t="s">
+      <c r="T32" s="10" t="s">
         <v>337</v>
       </c>
     </row>
@@ -2957,40 +3002,41 @@
         <v>32</v>
       </c>
       <c r="C33" s="2"/>
-      <c r="D33" s="1">
+      <c r="D33" s="9">
         <v>32</v>
       </c>
-      <c r="E33" s="3" t="s">
+      <c r="E33" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="G33" s="1">
+      <c r="F33" s="8"/>
+      <c r="G33" s="9">
         <v>32</v>
       </c>
-      <c r="H33" s="3" t="s">
+      <c r="H33" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="J33" s="1">
+      <c r="J33" s="9">
         <v>32</v>
       </c>
-      <c r="K33" s="2" t="s">
+      <c r="K33" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="M33" s="1">
+      <c r="M33" s="9">
         <v>32</v>
       </c>
-      <c r="N33" s="2" t="s">
+      <c r="N33" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="P33" s="1">
+      <c r="P33" s="9">
         <v>32</v>
       </c>
-      <c r="Q33" s="2" t="s">
+      <c r="Q33" s="6" t="s">
         <v>287</v>
       </c>
-      <c r="S33" s="1">
+      <c r="S33" s="9">
         <v>32</v>
       </c>
-      <c r="T33" s="3" t="s">
+      <c r="T33" s="10" t="s">
         <v>338</v>
       </c>
     </row>
@@ -3002,40 +3048,41 @@
         <v>33</v>
       </c>
       <c r="C34" s="2"/>
-      <c r="D34" s="1">
+      <c r="D34" s="9">
         <v>33</v>
       </c>
-      <c r="E34" s="3" t="s">
+      <c r="E34" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="G34" s="1">
+      <c r="F34" s="8"/>
+      <c r="G34" s="9">
         <v>33</v>
       </c>
-      <c r="H34" s="3" t="s">
+      <c r="H34" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="J34" s="1">
+      <c r="J34" s="9">
         <v>33</v>
       </c>
-      <c r="K34" s="2" t="s">
+      <c r="K34" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="M34" s="1">
+      <c r="M34" s="9">
         <v>33</v>
       </c>
-      <c r="N34" s="2" t="s">
+      <c r="N34" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="P34" s="1">
+      <c r="P34" s="9">
         <v>33</v>
       </c>
-      <c r="Q34" s="2" t="s">
+      <c r="Q34" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="S34" s="1">
+      <c r="S34" s="9">
         <v>33</v>
       </c>
-      <c r="T34" s="3" t="s">
+      <c r="T34" s="10" t="s">
         <v>339</v>
       </c>
     </row>
@@ -3047,40 +3094,41 @@
         <v>34</v>
       </c>
       <c r="C35" s="2"/>
-      <c r="D35" s="1">
+      <c r="D35" s="9">
         <v>34</v>
       </c>
-      <c r="E35" s="3" t="s">
+      <c r="E35" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="G35" s="1">
+      <c r="F35" s="8"/>
+      <c r="G35" s="9">
         <v>34</v>
       </c>
-      <c r="H35" s="3" t="s">
+      <c r="H35" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="J35" s="1">
+      <c r="J35" s="9">
         <v>34</v>
       </c>
-      <c r="K35" s="2" t="s">
+      <c r="K35" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="M35" s="1">
+      <c r="M35" s="9">
         <v>34</v>
       </c>
-      <c r="N35" s="2" t="s">
+      <c r="N35" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="P35" s="1">
+      <c r="P35" s="9">
         <v>34</v>
       </c>
-      <c r="Q35" s="2" t="s">
+      <c r="Q35" s="6" t="s">
         <v>289</v>
       </c>
-      <c r="S35" s="1">
+      <c r="S35" s="9">
         <v>34</v>
       </c>
-      <c r="T35" s="3" t="s">
+      <c r="T35" s="10" t="s">
         <v>340</v>
       </c>
     </row>
@@ -3092,40 +3140,41 @@
         <v>35</v>
       </c>
       <c r="C36" s="2"/>
-      <c r="D36" s="1">
+      <c r="D36" s="9">
         <v>35</v>
       </c>
-      <c r="E36" s="3" t="s">
+      <c r="E36" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="G36" s="1">
+      <c r="F36" s="8"/>
+      <c r="G36" s="9">
         <v>35</v>
       </c>
-      <c r="H36" s="3" t="s">
+      <c r="H36" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="J36" s="1">
+      <c r="J36" s="9">
         <v>35</v>
       </c>
-      <c r="K36" s="2" t="s">
+      <c r="K36" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="M36" s="1">
+      <c r="M36" s="9">
         <v>35</v>
       </c>
-      <c r="N36" s="2" t="s">
+      <c r="N36" s="6" t="s">
         <v>239</v>
       </c>
-      <c r="P36" s="1">
+      <c r="P36" s="9">
         <v>35</v>
       </c>
-      <c r="Q36" s="2" t="s">
+      <c r="Q36" s="6" t="s">
         <v>290</v>
       </c>
-      <c r="S36" s="1">
+      <c r="S36" s="9">
         <v>35</v>
       </c>
-      <c r="T36" s="3" t="s">
+      <c r="T36" s="10" t="s">
         <v>341</v>
       </c>
     </row>
@@ -3137,40 +3186,41 @@
         <v>36</v>
       </c>
       <c r="C37" s="2"/>
-      <c r="D37" s="1">
+      <c r="D37" s="9">
         <v>36</v>
       </c>
-      <c r="E37" s="3" t="s">
+      <c r="E37" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="G37" s="1">
+      <c r="F37" s="8"/>
+      <c r="G37" s="9">
         <v>36</v>
       </c>
-      <c r="H37" s="3" t="s">
+      <c r="H37" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="J37" s="1">
+      <c r="J37" s="9">
         <v>36</v>
       </c>
-      <c r="K37" s="2" t="s">
+      <c r="K37" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="M37" s="1">
+      <c r="M37" s="9">
         <v>36</v>
       </c>
-      <c r="N37" s="2" t="s">
+      <c r="N37" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="P37" s="1">
+      <c r="P37" s="9">
         <v>36</v>
       </c>
-      <c r="Q37" s="2" t="s">
+      <c r="Q37" s="6" t="s">
         <v>291</v>
       </c>
-      <c r="S37" s="1">
+      <c r="S37" s="9">
         <v>36</v>
       </c>
-      <c r="T37" s="3" t="s">
+      <c r="T37" s="10" t="s">
         <v>342</v>
       </c>
     </row>
@@ -3182,40 +3232,41 @@
         <v>37</v>
       </c>
       <c r="C38" s="2"/>
-      <c r="D38" s="1">
+      <c r="D38" s="9">
         <v>37</v>
       </c>
-      <c r="E38" s="3" t="s">
+      <c r="E38" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="G38" s="1">
+      <c r="F38" s="8"/>
+      <c r="G38" s="9">
         <v>37</v>
       </c>
-      <c r="H38" s="3" t="s">
+      <c r="H38" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="J38" s="1">
+      <c r="J38" s="9">
         <v>37</v>
       </c>
-      <c r="K38" s="2" t="s">
+      <c r="K38" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="M38" s="1">
+      <c r="M38" s="9">
         <v>37</v>
       </c>
-      <c r="N38" s="2" t="s">
+      <c r="N38" s="6" t="s">
         <v>241</v>
       </c>
-      <c r="P38" s="1">
+      <c r="P38" s="9">
         <v>37</v>
       </c>
-      <c r="Q38" s="2" t="s">
+      <c r="Q38" s="6" t="s">
         <v>292</v>
       </c>
-      <c r="S38" s="1">
+      <c r="S38" s="9">
         <v>37</v>
       </c>
-      <c r="T38" s="3" t="s">
+      <c r="T38" s="10" t="s">
         <v>343</v>
       </c>
     </row>
@@ -3227,40 +3278,41 @@
         <v>38</v>
       </c>
       <c r="C39" s="2"/>
-      <c r="D39" s="1">
+      <c r="D39" s="9">
         <v>38</v>
       </c>
-      <c r="E39" s="3" t="s">
+      <c r="E39" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="G39" s="1">
+      <c r="F39" s="8"/>
+      <c r="G39" s="9">
         <v>38</v>
       </c>
-      <c r="H39" s="3" t="s">
+      <c r="H39" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="J39" s="1">
+      <c r="J39" s="9">
         <v>38</v>
       </c>
-      <c r="K39" s="2" t="s">
+      <c r="K39" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="M39" s="1">
+      <c r="M39" s="9">
         <v>38</v>
       </c>
-      <c r="N39" s="2" t="s">
+      <c r="N39" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="P39" s="1">
+      <c r="P39" s="9">
         <v>38</v>
       </c>
-      <c r="Q39" s="2" t="s">
+      <c r="Q39" s="6" t="s">
         <v>293</v>
       </c>
-      <c r="S39" s="1">
+      <c r="S39" s="9">
         <v>38</v>
       </c>
-      <c r="T39" s="3" t="s">
+      <c r="T39" s="10" t="s">
         <v>344</v>
       </c>
     </row>
@@ -3272,40 +3324,41 @@
         <v>39</v>
       </c>
       <c r="C40" s="2"/>
-      <c r="D40" s="1">
+      <c r="D40" s="9">
         <v>39</v>
       </c>
-      <c r="E40" s="3" t="s">
+      <c r="E40" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="G40" s="1">
+      <c r="F40" s="8"/>
+      <c r="G40" s="9">
         <v>39</v>
       </c>
-      <c r="H40" s="3" t="s">
+      <c r="H40" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="J40" s="1">
+      <c r="J40" s="9">
         <v>39</v>
       </c>
-      <c r="K40" s="2" t="s">
+      <c r="K40" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="M40" s="1">
+      <c r="M40" s="9">
         <v>39</v>
       </c>
-      <c r="N40" s="2" t="s">
+      <c r="N40" s="6" t="s">
         <v>243</v>
       </c>
-      <c r="P40" s="1">
+      <c r="P40" s="9">
         <v>39</v>
       </c>
-      <c r="Q40" s="2" t="s">
+      <c r="Q40" s="6" t="s">
         <v>294</v>
       </c>
-      <c r="S40" s="1">
+      <c r="S40" s="9">
         <v>39</v>
       </c>
-      <c r="T40" s="3" t="s">
+      <c r="T40" s="10" t="s">
         <v>345</v>
       </c>
     </row>
@@ -3317,40 +3370,41 @@
         <v>40</v>
       </c>
       <c r="C41" s="2"/>
-      <c r="D41" s="1">
+      <c r="D41" s="9">
         <v>40</v>
       </c>
-      <c r="E41" s="3" t="s">
+      <c r="E41" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="G41" s="1">
+      <c r="F41" s="8"/>
+      <c r="G41" s="9">
         <v>40</v>
       </c>
-      <c r="H41" s="3" t="s">
+      <c r="H41" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="J41" s="1">
+      <c r="J41" s="9">
         <v>40</v>
       </c>
-      <c r="K41" s="2" t="s">
+      <c r="K41" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="M41" s="1">
+      <c r="M41" s="9">
         <v>40</v>
       </c>
-      <c r="N41" s="2" t="s">
+      <c r="N41" s="6" t="s">
         <v>244</v>
       </c>
-      <c r="P41" s="1">
+      <c r="P41" s="9">
         <v>40</v>
       </c>
-      <c r="Q41" s="2" t="s">
+      <c r="Q41" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="S41" s="1">
+      <c r="S41" s="9">
         <v>40</v>
       </c>
-      <c r="T41" s="3" t="s">
+      <c r="T41" s="10" t="s">
         <v>346</v>
       </c>
     </row>
@@ -3362,40 +3416,41 @@
         <v>41</v>
       </c>
       <c r="C42" s="2"/>
-      <c r="D42" s="1">
+      <c r="D42" s="9">
         <v>41</v>
       </c>
-      <c r="E42" s="3" t="s">
+      <c r="E42" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="G42" s="1">
+      <c r="F42" s="8"/>
+      <c r="G42" s="9">
         <v>41</v>
       </c>
-      <c r="H42" s="3" t="s">
+      <c r="H42" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="J42" s="1">
+      <c r="J42" s="9">
         <v>41</v>
       </c>
-      <c r="K42" s="2" t="s">
+      <c r="K42" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="M42" s="1">
+      <c r="M42" s="9">
         <v>41</v>
       </c>
-      <c r="N42" s="2" t="s">
+      <c r="N42" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="P42" s="1">
+      <c r="P42" s="9">
         <v>41</v>
       </c>
-      <c r="Q42" s="2" t="s">
+      <c r="Q42" s="6" t="s">
         <v>296</v>
       </c>
-      <c r="S42" s="1">
+      <c r="S42" s="9">
         <v>41</v>
       </c>
-      <c r="T42" s="3" t="s">
+      <c r="T42" s="10" t="s">
         <v>347</v>
       </c>
     </row>
@@ -3407,40 +3462,41 @@
         <v>42</v>
       </c>
       <c r="C43" s="2"/>
-      <c r="D43" s="1">
+      <c r="D43" s="9">
         <v>42</v>
       </c>
-      <c r="E43" s="3" t="s">
+      <c r="E43" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="G43" s="1">
+      <c r="F43" s="8"/>
+      <c r="G43" s="9">
         <v>42</v>
       </c>
-      <c r="H43" s="3" t="s">
+      <c r="H43" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="J43" s="1">
+      <c r="J43" s="9">
         <v>42</v>
       </c>
-      <c r="K43" s="2" t="s">
+      <c r="K43" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="M43" s="1">
+      <c r="M43" s="9">
         <v>42</v>
       </c>
-      <c r="N43" s="2" t="s">
+      <c r="N43" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="P43" s="1">
+      <c r="P43" s="9">
         <v>42</v>
       </c>
-      <c r="Q43" s="2" t="s">
+      <c r="Q43" s="6" t="s">
         <v>297</v>
       </c>
-      <c r="S43" s="1">
+      <c r="S43" s="9">
         <v>42</v>
       </c>
-      <c r="T43" s="3" t="s">
+      <c r="T43" s="10" t="s">
         <v>348</v>
       </c>
     </row>
@@ -3452,40 +3508,41 @@
         <v>43</v>
       </c>
       <c r="C44" s="2"/>
-      <c r="D44" s="1">
+      <c r="D44" s="9">
         <v>43</v>
       </c>
-      <c r="E44" s="3" t="s">
+      <c r="E44" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="G44" s="1">
+      <c r="F44" s="8"/>
+      <c r="G44" s="9">
         <v>43</v>
       </c>
-      <c r="H44" s="3" t="s">
+      <c r="H44" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="J44" s="1">
+      <c r="J44" s="9">
         <v>43</v>
       </c>
-      <c r="K44" s="2" t="s">
+      <c r="K44" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="M44" s="1">
+      <c r="M44" s="9">
         <v>43</v>
       </c>
-      <c r="N44" s="2" t="s">
+      <c r="N44" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="P44" s="1">
+      <c r="P44" s="9">
         <v>43</v>
       </c>
-      <c r="Q44" s="2" t="s">
+      <c r="Q44" s="6" t="s">
         <v>298</v>
       </c>
-      <c r="S44" s="1">
+      <c r="S44" s="9">
         <v>43</v>
       </c>
-      <c r="T44" s="3" t="s">
+      <c r="T44" s="10" t="s">
         <v>349</v>
       </c>
     </row>
@@ -3497,40 +3554,41 @@
         <v>44</v>
       </c>
       <c r="C45" s="2"/>
-      <c r="D45" s="1">
+      <c r="D45" s="9">
         <v>44</v>
       </c>
-      <c r="E45" s="3" t="s">
+      <c r="E45" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="G45" s="1">
+      <c r="F45" s="8"/>
+      <c r="G45" s="9">
         <v>44</v>
       </c>
-      <c r="H45" s="3" t="s">
+      <c r="H45" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="J45" s="1">
+      <c r="J45" s="9">
         <v>44</v>
       </c>
-      <c r="K45" s="2" t="s">
+      <c r="K45" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="M45" s="1">
+      <c r="M45" s="9">
         <v>44</v>
       </c>
-      <c r="N45" s="2" t="s">
+      <c r="N45" s="6" t="s">
         <v>248</v>
       </c>
-      <c r="P45" s="1">
+      <c r="P45" s="9">
         <v>44</v>
       </c>
-      <c r="Q45" s="2" t="s">
+      <c r="Q45" s="6" t="s">
         <v>299</v>
       </c>
-      <c r="S45" s="1">
+      <c r="S45" s="9">
         <v>44</v>
       </c>
-      <c r="T45" s="3" t="s">
+      <c r="T45" s="10" t="s">
         <v>350</v>
       </c>
     </row>
@@ -3542,40 +3600,41 @@
         <v>45</v>
       </c>
       <c r="C46" s="2"/>
-      <c r="D46" s="1">
+      <c r="D46" s="9">
         <v>45</v>
       </c>
-      <c r="E46" s="3" t="s">
+      <c r="E46" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="G46" s="1">
+      <c r="F46" s="8"/>
+      <c r="G46" s="9">
         <v>45</v>
       </c>
-      <c r="H46" s="3" t="s">
+      <c r="H46" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="J46" s="1">
+      <c r="J46" s="9">
         <v>45</v>
       </c>
-      <c r="K46" s="2" t="s">
+      <c r="K46" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="M46" s="1">
+      <c r="M46" s="9">
         <v>45</v>
       </c>
-      <c r="N46" s="2" t="s">
+      <c r="N46" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="P46" s="1">
+      <c r="P46" s="9">
         <v>45</v>
       </c>
-      <c r="Q46" s="2" t="s">
+      <c r="Q46" s="6" t="s">
         <v>300</v>
       </c>
-      <c r="S46" s="1">
+      <c r="S46" s="9">
         <v>45</v>
       </c>
-      <c r="T46" s="3" t="s">
+      <c r="T46" s="10" t="s">
         <v>351</v>
       </c>
     </row>
@@ -3587,40 +3646,41 @@
         <v>46</v>
       </c>
       <c r="C47" s="2"/>
-      <c r="D47" s="1">
+      <c r="D47" s="9">
         <v>46</v>
       </c>
-      <c r="E47" s="2" t="s">
+      <c r="E47" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="G47" s="1">
+      <c r="F47" s="8"/>
+      <c r="G47" s="9">
         <v>46</v>
       </c>
-      <c r="H47" s="3" t="s">
+      <c r="H47" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="J47" s="1">
+      <c r="J47" s="9">
         <v>46</v>
       </c>
-      <c r="K47" s="2" t="s">
+      <c r="K47" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="M47" s="1">
+      <c r="M47" s="9">
         <v>46</v>
       </c>
-      <c r="N47" s="2" t="s">
+      <c r="N47" s="6" t="s">
         <v>250</v>
       </c>
-      <c r="P47" s="1">
+      <c r="P47" s="9">
         <v>46</v>
       </c>
-      <c r="Q47" s="2" t="s">
+      <c r="Q47" s="6" t="s">
         <v>301</v>
       </c>
-      <c r="S47" s="1">
+      <c r="S47" s="9">
         <v>46</v>
       </c>
-      <c r="T47" s="3" t="s">
+      <c r="T47" s="10" t="s">
         <v>352</v>
       </c>
     </row>
@@ -3632,40 +3692,41 @@
         <v>47</v>
       </c>
       <c r="C48" s="2"/>
-      <c r="D48" s="1">
+      <c r="D48" s="9">
         <v>47</v>
       </c>
-      <c r="E48" s="2" t="s">
+      <c r="E48" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="G48" s="1">
+      <c r="F48" s="8"/>
+      <c r="G48" s="9">
         <v>47</v>
       </c>
-      <c r="H48" s="3" t="s">
+      <c r="H48" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="J48" s="1">
+      <c r="J48" s="9">
         <v>47</v>
       </c>
-      <c r="K48" s="2" t="s">
+      <c r="K48" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="M48" s="1">
+      <c r="M48" s="9">
         <v>47</v>
       </c>
-      <c r="N48" s="2" t="s">
+      <c r="N48" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="P48" s="1">
+      <c r="P48" s="9">
         <v>47</v>
       </c>
-      <c r="Q48" s="2" t="s">
+      <c r="Q48" s="6" t="s">
         <v>302</v>
       </c>
-      <c r="S48" s="1">
+      <c r="S48" s="9">
         <v>47</v>
       </c>
-      <c r="T48" s="3" t="s">
+      <c r="T48" s="10" t="s">
         <v>353</v>
       </c>
     </row>
@@ -3677,40 +3738,41 @@
         <v>48</v>
       </c>
       <c r="C49" s="2"/>
-      <c r="D49" s="1">
+      <c r="D49" s="9">
         <v>48</v>
       </c>
-      <c r="E49" s="2" t="s">
+      <c r="E49" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="G49" s="1">
+      <c r="F49" s="8"/>
+      <c r="G49" s="9">
         <v>48</v>
       </c>
-      <c r="H49" s="3" t="s">
+      <c r="H49" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="J49" s="1">
+      <c r="J49" s="9">
         <v>48</v>
       </c>
-      <c r="K49" s="2" t="s">
+      <c r="K49" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="M49" s="1">
+      <c r="M49" s="9">
         <v>48</v>
       </c>
-      <c r="N49" s="2" t="s">
+      <c r="N49" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="P49" s="1">
+      <c r="P49" s="9">
         <v>48</v>
       </c>
-      <c r="Q49" s="2" t="s">
+      <c r="Q49" s="6" t="s">
         <v>303</v>
       </c>
-      <c r="S49" s="1">
+      <c r="S49" s="9">
         <v>48</v>
       </c>
-      <c r="T49" s="3" t="s">
+      <c r="T49" s="10" t="s">
         <v>354</v>
       </c>
     </row>
@@ -3722,40 +3784,41 @@
         <v>49</v>
       </c>
       <c r="C50" s="2"/>
-      <c r="D50" s="1">
+      <c r="D50" s="9">
         <v>49</v>
       </c>
-      <c r="E50" s="2" t="s">
+      <c r="E50" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="G50" s="1">
+      <c r="F50" s="8"/>
+      <c r="G50" s="9">
         <v>49</v>
       </c>
-      <c r="H50" s="3" t="s">
+      <c r="H50" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="J50" s="1">
+      <c r="J50" s="9">
         <v>49</v>
       </c>
-      <c r="K50" s="2" t="s">
+      <c r="K50" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="M50" s="1">
+      <c r="M50" s="9">
         <v>49</v>
       </c>
-      <c r="N50" s="2" t="s">
+      <c r="N50" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="P50" s="1">
+      <c r="P50" s="9">
         <v>49</v>
       </c>
-      <c r="Q50" s="2" t="s">
+      <c r="Q50" s="6" t="s">
         <v>304</v>
       </c>
-      <c r="S50" s="1">
+      <c r="S50" s="9">
         <v>49</v>
       </c>
-      <c r="T50" s="3" t="s">
+      <c r="T50" s="10" t="s">
         <v>355</v>
       </c>
     </row>
@@ -3767,40 +3830,41 @@
         <v>50</v>
       </c>
       <c r="C51" s="2"/>
-      <c r="D51" s="1">
+      <c r="D51" s="9">
         <v>50</v>
       </c>
-      <c r="E51" s="2" t="s">
+      <c r="E51" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="G51" s="1">
+      <c r="F51" s="8"/>
+      <c r="G51" s="9">
         <v>50</v>
       </c>
-      <c r="H51" s="3" t="s">
+      <c r="H51" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="J51" s="1">
+      <c r="J51" s="9">
         <v>50</v>
       </c>
-      <c r="K51" s="2" t="s">
+      <c r="K51" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="M51" s="1">
+      <c r="M51" s="9">
         <v>50</v>
       </c>
-      <c r="N51" s="2" t="s">
+      <c r="N51" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="P51" s="1">
+      <c r="P51" s="9">
         <v>50</v>
       </c>
-      <c r="Q51" s="2" t="s">
+      <c r="Q51" s="6" t="s">
         <v>305</v>
       </c>
-      <c r="S51" s="1">
+      <c r="S51" s="9">
         <v>50</v>
       </c>
-      <c r="T51" s="3" t="s">
+      <c r="T51" s="10" t="s">
         <v>356</v>
       </c>
     </row>

--- a/SoSerial.xlsx
+++ b/SoSerial.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\HK2Nam2\PTTKHTTT\DoAn\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01AB45D3-6F19-4689-8594-4753FAEFF472}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B5D930B-CE8A-46D3-8757-2549589CCBD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AEEAB626-5BEE-420A-A42D-F78A94A6DE5E}"/>
   </bookViews>
@@ -1179,7 +1179,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
@@ -1196,17 +1196,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1567,31 +1557,30 @@
         <v>0</v>
       </c>
       <c r="B1" s="5"/>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="E1" s="7"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="7" t="s">
+      <c r="E1" s="5"/>
+      <c r="G1" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="H1" s="7"/>
-      <c r="J1" s="7" t="s">
+      <c r="H1" s="5"/>
+      <c r="J1" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="K1" s="7"/>
-      <c r="M1" s="7" t="s">
+      <c r="K1" s="5"/>
+      <c r="M1" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="N1" s="7"/>
-      <c r="P1" s="7" t="s">
+      <c r="N1" s="5"/>
+      <c r="P1" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="Q1" s="7"/>
-      <c r="S1" s="7" t="s">
+      <c r="Q1" s="5"/>
+      <c r="S1" s="5" t="s">
         <v>306</v>
       </c>
-      <c r="T1" s="7"/>
+      <c r="T1" s="5"/>
     </row>
     <row r="2" spans="1:20" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
@@ -1600,38 +1589,37 @@
       <c r="B2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="9">
+      <c r="D2" s="1">
         <v>1</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="F2" s="8"/>
-      <c r="G2" s="9">
+      <c r="G2" s="1">
         <v>1</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="J2" s="9">
+      <c r="J2" s="1">
         <v>1</v>
       </c>
       <c r="K2" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="M2" s="9">
+      <c r="M2" s="1">
         <v>1</v>
       </c>
       <c r="N2" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="P2" s="9">
+      <c r="P2" s="1">
         <v>1</v>
       </c>
       <c r="Q2" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="S2" s="9">
+      <c r="S2" s="1">
         <v>1</v>
       </c>
       <c r="T2" s="4" t="s">
@@ -1645,38 +1633,37 @@
       <c r="B3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="9">
+      <c r="D3" s="1">
         <v>2</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="F3" s="8"/>
-      <c r="G3" s="9">
+      <c r="G3" s="1">
         <v>2</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="J3" s="9">
+      <c r="J3" s="1">
         <v>2</v>
       </c>
       <c r="K3" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="M3" s="9">
+      <c r="M3" s="1">
         <v>2</v>
       </c>
       <c r="N3" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="P3" s="9">
+      <c r="P3" s="1">
         <v>2</v>
       </c>
       <c r="Q3" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="S3" s="9">
+      <c r="S3" s="1">
         <v>2</v>
       </c>
       <c r="T3" s="4" t="s">
@@ -1690,38 +1677,37 @@
       <c r="B4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="9">
+      <c r="D4" s="1">
         <v>3</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="F4" s="8"/>
-      <c r="G4" s="9">
+      <c r="G4" s="1">
         <v>3</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="J4" s="9">
+      <c r="J4" s="1">
         <v>3</v>
       </c>
       <c r="K4" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="M4" s="9">
+      <c r="M4" s="1">
         <v>3</v>
       </c>
       <c r="N4" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="P4" s="9">
+      <c r="P4" s="1">
         <v>3</v>
       </c>
       <c r="Q4" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="S4" s="9">
+      <c r="S4" s="1">
         <v>3</v>
       </c>
       <c r="T4" s="4" t="s">
@@ -1735,38 +1721,37 @@
       <c r="B5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="1">
         <v>4</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="F5" s="8"/>
-      <c r="G5" s="9">
+      <c r="G5" s="1">
         <v>4</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="J5" s="9">
+      <c r="J5" s="1">
         <v>4</v>
       </c>
       <c r="K5" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="M5" s="9">
+      <c r="M5" s="1">
         <v>4</v>
       </c>
       <c r="N5" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="P5" s="9">
+      <c r="P5" s="1">
         <v>4</v>
       </c>
       <c r="Q5" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="S5" s="9">
+      <c r="S5" s="1">
         <v>4</v>
       </c>
       <c r="T5" s="4" t="s">
@@ -1780,38 +1765,37 @@
       <c r="B6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="1">
         <v>5</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="F6" s="8"/>
-      <c r="G6" s="9">
+      <c r="G6" s="1">
         <v>5</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="J6" s="9">
+      <c r="J6" s="1">
         <v>5</v>
       </c>
       <c r="K6" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="M6" s="9">
+      <c r="M6" s="1">
         <v>5</v>
       </c>
       <c r="N6" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="P6" s="9">
+      <c r="P6" s="1">
         <v>5</v>
       </c>
       <c r="Q6" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="S6" s="9">
+      <c r="S6" s="1">
         <v>5</v>
       </c>
       <c r="T6" s="4" t="s">
@@ -1825,41 +1809,40 @@
       <c r="B7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="9">
+      <c r="D7" s="1">
         <v>6</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="F7" s="8"/>
-      <c r="G7" s="9">
+      <c r="G7" s="1">
         <v>6</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="J7" s="9">
+      <c r="J7" s="1">
         <v>6</v>
       </c>
       <c r="K7" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="M7" s="9">
+      <c r="M7" s="1">
         <v>6</v>
       </c>
       <c r="N7" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="P7" s="9">
+      <c r="P7" s="1">
         <v>6</v>
       </c>
       <c r="Q7" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="S7" s="9">
+      <c r="S7" s="1">
         <v>6</v>
       </c>
-      <c r="T7" s="6" t="s">
+      <c r="T7" s="2" t="s">
         <v>312</v>
       </c>
     </row>
@@ -1870,41 +1853,40 @@
       <c r="B8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="9">
+      <c r="D8" s="1">
         <v>7</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="F8" s="8"/>
-      <c r="G8" s="9">
+      <c r="G8" s="1">
         <v>7</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="J8" s="9">
+      <c r="J8" s="1">
         <v>7</v>
       </c>
       <c r="K8" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="M8" s="9">
+      <c r="M8" s="1">
         <v>7</v>
       </c>
       <c r="N8" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="P8" s="9">
+      <c r="P8" s="1">
         <v>7</v>
       </c>
       <c r="Q8" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="S8" s="9">
+      <c r="S8" s="1">
         <v>7</v>
       </c>
-      <c r="T8" s="6" t="s">
+      <c r="T8" s="2" t="s">
         <v>313</v>
       </c>
     </row>
@@ -1915,41 +1897,40 @@
       <c r="B9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="9">
+      <c r="D9" s="1">
         <v>8</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="F9" s="8"/>
-      <c r="G9" s="9">
+      <c r="G9" s="1">
         <v>8</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="J9" s="9">
+      <c r="J9" s="1">
         <v>8</v>
       </c>
       <c r="K9" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="M9" s="9">
+      <c r="M9" s="1">
         <v>8</v>
       </c>
       <c r="N9" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="P9" s="9">
+      <c r="P9" s="1">
         <v>8</v>
       </c>
       <c r="Q9" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="S9" s="9">
+      <c r="S9" s="1">
         <v>8</v>
       </c>
-      <c r="T9" s="6" t="s">
+      <c r="T9" s="2" t="s">
         <v>314</v>
       </c>
     </row>
@@ -1960,41 +1941,40 @@
       <c r="B10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="9">
+      <c r="D10" s="1">
         <v>9</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="F10" s="8"/>
-      <c r="G10" s="9">
+      <c r="G10" s="1">
         <v>9</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="J10" s="9">
+      <c r="J10" s="1">
         <v>9</v>
       </c>
       <c r="K10" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="M10" s="9">
+      <c r="M10" s="1">
         <v>9</v>
       </c>
       <c r="N10" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="P10" s="9">
+      <c r="P10" s="1">
         <v>9</v>
       </c>
       <c r="Q10" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="S10" s="9">
+      <c r="S10" s="1">
         <v>9</v>
       </c>
-      <c r="T10" s="6" t="s">
+      <c r="T10" s="2" t="s">
         <v>315</v>
       </c>
     </row>
@@ -2005,41 +1985,40 @@
       <c r="B11" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="9">
+      <c r="D11" s="1">
         <v>10</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="F11" s="8"/>
-      <c r="G11" s="9">
+      <c r="G11" s="1">
         <v>10</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="J11" s="9">
+      <c r="J11" s="1">
         <v>10</v>
       </c>
       <c r="K11" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="M11" s="9">
+      <c r="M11" s="1">
         <v>10</v>
       </c>
       <c r="N11" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="P11" s="9">
+      <c r="P11" s="1">
         <v>10</v>
       </c>
       <c r="Q11" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="S11" s="9">
+      <c r="S11" s="1">
         <v>10</v>
       </c>
-      <c r="T11" s="6" t="s">
+      <c r="T11" s="2" t="s">
         <v>316</v>
       </c>
     </row>
@@ -2050,41 +2029,40 @@
       <c r="B12" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="9">
+      <c r="D12" s="1">
         <v>11</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="F12" s="8"/>
-      <c r="G12" s="9">
+      <c r="G12" s="1">
         <v>11</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="J12" s="9">
+      <c r="J12" s="1">
         <v>11</v>
       </c>
       <c r="K12" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="M12" s="9">
+      <c r="M12" s="1">
         <v>11</v>
       </c>
       <c r="N12" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="P12" s="9">
+      <c r="P12" s="1">
         <v>11</v>
       </c>
-      <c r="Q12" s="6" t="s">
+      <c r="Q12" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="S12" s="9">
+      <c r="S12" s="1">
         <v>11</v>
       </c>
-      <c r="T12" s="6" t="s">
+      <c r="T12" s="2" t="s">
         <v>317</v>
       </c>
     </row>
@@ -2095,41 +2073,40 @@
       <c r="B13" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="9">
+      <c r="D13" s="1">
         <v>12</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="F13" s="8"/>
-      <c r="G13" s="9">
+      <c r="G13" s="1">
         <v>12</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="J13" s="9">
+      <c r="J13" s="1">
         <v>12</v>
       </c>
       <c r="K13" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="M13" s="9">
+      <c r="M13" s="1">
         <v>12</v>
       </c>
       <c r="N13" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="P13" s="9">
+      <c r="P13" s="1">
         <v>12</v>
       </c>
-      <c r="Q13" s="6" t="s">
+      <c r="Q13" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="S13" s="9">
+      <c r="S13" s="1">
         <v>12</v>
       </c>
-      <c r="T13" s="6" t="s">
+      <c r="T13" s="2" t="s">
         <v>318</v>
       </c>
     </row>
@@ -2140,41 +2117,40 @@
       <c r="B14" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D14" s="9">
+      <c r="D14" s="1">
         <v>13</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="F14" s="8"/>
-      <c r="G14" s="9">
+      <c r="G14" s="1">
         <v>13</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="J14" s="9">
+      <c r="J14" s="1">
         <v>13</v>
       </c>
       <c r="K14" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="M14" s="9">
+      <c r="M14" s="1">
         <v>13</v>
       </c>
       <c r="N14" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="P14" s="9">
+      <c r="P14" s="1">
         <v>13</v>
       </c>
-      <c r="Q14" s="6" t="s">
+      <c r="Q14" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="S14" s="9">
+      <c r="S14" s="1">
         <v>13</v>
       </c>
-      <c r="T14" s="6" t="s">
+      <c r="T14" s="2" t="s">
         <v>319</v>
       </c>
     </row>
@@ -2185,41 +2161,40 @@
       <c r="B15" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="9">
+      <c r="D15" s="1">
         <v>14</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="F15" s="8"/>
-      <c r="G15" s="9">
+      <c r="G15" s="1">
         <v>14</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="J15" s="9">
+      <c r="J15" s="1">
         <v>14</v>
       </c>
-      <c r="K15" s="6" t="s">
+      <c r="K15" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="M15" s="9">
+      <c r="M15" s="1">
         <v>14</v>
       </c>
       <c r="N15" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="P15" s="9">
+      <c r="P15" s="1">
         <v>14</v>
       </c>
-      <c r="Q15" s="6" t="s">
+      <c r="Q15" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="S15" s="9">
+      <c r="S15" s="1">
         <v>14</v>
       </c>
-      <c r="T15" s="6" t="s">
+      <c r="T15" s="2" t="s">
         <v>320</v>
       </c>
     </row>
@@ -2230,41 +2205,40 @@
       <c r="B16" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D16" s="9">
+      <c r="D16" s="1">
         <v>15</v>
       </c>
       <c r="E16" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="F16" s="8"/>
-      <c r="G16" s="9">
+      <c r="G16" s="1">
         <v>15</v>
       </c>
       <c r="H16" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="J16" s="9">
+      <c r="J16" s="1">
         <v>15</v>
       </c>
-      <c r="K16" s="6" t="s">
+      <c r="K16" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="M16" s="9">
+      <c r="M16" s="1">
         <v>15</v>
       </c>
       <c r="N16" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="P16" s="9">
+      <c r="P16" s="1">
         <v>15</v>
       </c>
-      <c r="Q16" s="6" t="s">
+      <c r="Q16" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="S16" s="9">
+      <c r="S16" s="1">
         <v>15</v>
       </c>
-      <c r="T16" s="6" t="s">
+      <c r="T16" s="2" t="s">
         <v>321</v>
       </c>
     </row>
@@ -2275,41 +2249,40 @@
       <c r="B17" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D17" s="9">
+      <c r="D17" s="1">
         <v>16</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="F17" s="8"/>
-      <c r="G17" s="9">
+      <c r="G17" s="1">
         <v>16</v>
       </c>
       <c r="H17" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="J17" s="9">
+      <c r="J17" s="1">
         <v>16</v>
       </c>
-      <c r="K17" s="6" t="s">
+      <c r="K17" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="M17" s="9">
+      <c r="M17" s="1">
         <v>16</v>
       </c>
       <c r="N17" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="P17" s="9">
+      <c r="P17" s="1">
         <v>16</v>
       </c>
-      <c r="Q17" s="6" t="s">
+      <c r="Q17" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="S17" s="9">
+      <c r="S17" s="1">
         <v>16</v>
       </c>
-      <c r="T17" s="6" t="s">
+      <c r="T17" s="2" t="s">
         <v>322</v>
       </c>
     </row>
@@ -2320,41 +2293,40 @@
       <c r="B18" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D18" s="9">
+      <c r="D18" s="1">
         <v>17</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="F18" s="8"/>
-      <c r="G18" s="9">
+      <c r="G18" s="1">
         <v>17</v>
       </c>
       <c r="H18" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="J18" s="9">
+      <c r="J18" s="1">
         <v>17</v>
       </c>
-      <c r="K18" s="6" t="s">
+      <c r="K18" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="M18" s="9">
+      <c r="M18" s="1">
         <v>17</v>
       </c>
       <c r="N18" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="P18" s="9">
+      <c r="P18" s="1">
         <v>17</v>
       </c>
-      <c r="Q18" s="6" t="s">
+      <c r="Q18" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="S18" s="9">
+      <c r="S18" s="1">
         <v>17</v>
       </c>
-      <c r="T18" s="6" t="s">
+      <c r="T18" s="2" t="s">
         <v>323</v>
       </c>
     </row>
@@ -2365,41 +2337,40 @@
       <c r="B19" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D19" s="9">
+      <c r="D19" s="1">
         <v>18</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="F19" s="8"/>
-      <c r="G19" s="9">
+      <c r="G19" s="1">
         <v>18</v>
       </c>
       <c r="H19" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="J19" s="9">
+      <c r="J19" s="1">
         <v>18</v>
       </c>
-      <c r="K19" s="6" t="s">
+      <c r="K19" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="M19" s="9">
+      <c r="M19" s="1">
         <v>18</v>
       </c>
       <c r="N19" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="P19" s="9">
+      <c r="P19" s="1">
         <v>18</v>
       </c>
-      <c r="Q19" s="6" t="s">
+      <c r="Q19" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="S19" s="9">
+      <c r="S19" s="1">
         <v>18</v>
       </c>
-      <c r="T19" s="6" t="s">
+      <c r="T19" s="2" t="s">
         <v>324</v>
       </c>
     </row>
@@ -2410,41 +2381,40 @@
       <c r="B20" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D20" s="9">
+      <c r="D20" s="1">
         <v>19</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="F20" s="8"/>
-      <c r="G20" s="9">
+      <c r="G20" s="1">
         <v>19</v>
       </c>
-      <c r="H20" s="6" t="s">
+      <c r="H20" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="J20" s="9">
+      <c r="J20" s="1">
         <v>19</v>
       </c>
-      <c r="K20" s="6" t="s">
+      <c r="K20" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="M20" s="9">
+      <c r="M20" s="1">
         <v>19</v>
       </c>
       <c r="N20" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="P20" s="9">
+      <c r="P20" s="1">
         <v>19</v>
       </c>
-      <c r="Q20" s="6" t="s">
+      <c r="Q20" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="S20" s="9">
+      <c r="S20" s="1">
         <v>19</v>
       </c>
-      <c r="T20" s="6" t="s">
+      <c r="T20" s="2" t="s">
         <v>325</v>
       </c>
     </row>
@@ -2455,41 +2425,40 @@
       <c r="B21" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D21" s="9">
+      <c r="D21" s="1">
         <v>20</v>
       </c>
       <c r="E21" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="F21" s="8"/>
-      <c r="G21" s="9">
+      <c r="G21" s="1">
         <v>20</v>
       </c>
-      <c r="H21" s="6" t="s">
+      <c r="H21" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="J21" s="9">
+      <c r="J21" s="1">
         <v>20</v>
       </c>
-      <c r="K21" s="6" t="s">
+      <c r="K21" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="M21" s="9">
+      <c r="M21" s="1">
         <v>20</v>
       </c>
       <c r="N21" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="P21" s="9">
+      <c r="P21" s="1">
         <v>20</v>
       </c>
-      <c r="Q21" s="6" t="s">
+      <c r="Q21" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="S21" s="9">
+      <c r="S21" s="1">
         <v>20</v>
       </c>
-      <c r="T21" s="6" t="s">
+      <c r="T21" s="2" t="s">
         <v>326</v>
       </c>
     </row>
@@ -2497,44 +2466,43 @@
       <c r="A22" s="1">
         <v>21</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D22" s="9">
+      <c r="D22" s="1">
         <v>21</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="F22" s="8"/>
-      <c r="G22" s="9">
+      <c r="G22" s="1">
         <v>21</v>
       </c>
-      <c r="H22" s="6" t="s">
+      <c r="H22" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="J22" s="9">
+      <c r="J22" s="1">
         <v>21</v>
       </c>
-      <c r="K22" s="6" t="s">
+      <c r="K22" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="M22" s="9">
+      <c r="M22" s="1">
         <v>21</v>
       </c>
-      <c r="N22" s="6" t="s">
+      <c r="N22" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="P22" s="9">
+      <c r="P22" s="1">
         <v>21</v>
       </c>
-      <c r="Q22" s="6" t="s">
+      <c r="Q22" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="S22" s="9">
+      <c r="S22" s="1">
         <v>21</v>
       </c>
-      <c r="T22" s="6" t="s">
+      <c r="T22" s="2" t="s">
         <v>327</v>
       </c>
     </row>
@@ -2542,44 +2510,43 @@
       <c r="A23" s="1">
         <v>22</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D23" s="9">
+      <c r="D23" s="1">
         <v>22</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="F23" s="8"/>
-      <c r="G23" s="9">
+      <c r="G23" s="1">
         <v>22</v>
       </c>
-      <c r="H23" s="6" t="s">
+      <c r="H23" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="J23" s="9">
+      <c r="J23" s="1">
         <v>22</v>
       </c>
-      <c r="K23" s="6" t="s">
+      <c r="K23" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="M23" s="9">
+      <c r="M23" s="1">
         <v>22</v>
       </c>
-      <c r="N23" s="6" t="s">
+      <c r="N23" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="P23" s="9">
+      <c r="P23" s="1">
         <v>22</v>
       </c>
-      <c r="Q23" s="6" t="s">
+      <c r="Q23" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="S23" s="9">
+      <c r="S23" s="1">
         <v>22</v>
       </c>
-      <c r="T23" s="6" t="s">
+      <c r="T23" s="2" t="s">
         <v>328</v>
       </c>
     </row>
@@ -2587,44 +2554,43 @@
       <c r="A24" s="1">
         <v>23</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D24" s="9">
+      <c r="D24" s="1">
         <v>23</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="F24" s="8"/>
-      <c r="G24" s="9">
+      <c r="G24" s="1">
         <v>23</v>
       </c>
-      <c r="H24" s="6" t="s">
+      <c r="H24" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="J24" s="9">
+      <c r="J24" s="1">
         <v>23</v>
       </c>
-      <c r="K24" s="6" t="s">
+      <c r="K24" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="M24" s="9">
+      <c r="M24" s="1">
         <v>23</v>
       </c>
-      <c r="N24" s="6" t="s">
+      <c r="N24" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="P24" s="9">
+      <c r="P24" s="1">
         <v>23</v>
       </c>
-      <c r="Q24" s="6" t="s">
+      <c r="Q24" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="S24" s="9">
+      <c r="S24" s="1">
         <v>23</v>
       </c>
-      <c r="T24" s="6" t="s">
+      <c r="T24" s="2" t="s">
         <v>329</v>
       </c>
     </row>
@@ -2632,44 +2598,43 @@
       <c r="A25" s="1">
         <v>24</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D25" s="9">
+      <c r="D25" s="1">
         <v>24</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="F25" s="8"/>
-      <c r="G25" s="9">
+      <c r="G25" s="1">
         <v>24</v>
       </c>
-      <c r="H25" s="6" t="s">
+      <c r="H25" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="J25" s="9">
+      <c r="J25" s="1">
         <v>24</v>
       </c>
-      <c r="K25" s="6" t="s">
+      <c r="K25" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="M25" s="9">
+      <c r="M25" s="1">
         <v>24</v>
       </c>
-      <c r="N25" s="6" t="s">
+      <c r="N25" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="P25" s="9">
+      <c r="P25" s="1">
         <v>24</v>
       </c>
-      <c r="Q25" s="6" t="s">
+      <c r="Q25" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="S25" s="9">
+      <c r="S25" s="1">
         <v>24</v>
       </c>
-      <c r="T25" s="6" t="s">
+      <c r="T25" s="2" t="s">
         <v>330</v>
       </c>
     </row>
@@ -2677,44 +2642,43 @@
       <c r="A26" s="1">
         <v>25</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D26" s="9">
+      <c r="D26" s="1">
         <v>25</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="F26" s="8"/>
-      <c r="G26" s="9">
+      <c r="G26" s="1">
         <v>25</v>
       </c>
-      <c r="H26" s="6" t="s">
+      <c r="H26" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="J26" s="9">
+      <c r="J26" s="1">
         <v>25</v>
       </c>
-      <c r="K26" s="6" t="s">
+      <c r="K26" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="M26" s="9">
+      <c r="M26" s="1">
         <v>25</v>
       </c>
-      <c r="N26" s="6" t="s">
+      <c r="N26" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="P26" s="9">
+      <c r="P26" s="1">
         <v>25</v>
       </c>
-      <c r="Q26" s="6" t="s">
+      <c r="Q26" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="S26" s="9">
+      <c r="S26" s="1">
         <v>25</v>
       </c>
-      <c r="T26" s="6" t="s">
+      <c r="T26" s="2" t="s">
         <v>331</v>
       </c>
     </row>
@@ -2722,45 +2686,44 @@
       <c r="A27" s="1">
         <v>26</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="6" t="s">
         <v>26</v>
       </c>
       <c r="C27" s="2"/>
-      <c r="D27" s="9">
+      <c r="D27" s="1">
         <v>26</v>
       </c>
-      <c r="E27" s="6" t="s">
+      <c r="E27" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="F27" s="8"/>
-      <c r="G27" s="9">
+      <c r="G27" s="1">
         <v>26</v>
       </c>
-      <c r="H27" s="10" t="s">
+      <c r="H27" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="J27" s="9">
+      <c r="J27" s="1">
         <v>26</v>
       </c>
-      <c r="K27" s="6" t="s">
+      <c r="K27" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="M27" s="9">
+      <c r="M27" s="1">
         <v>26</v>
       </c>
-      <c r="N27" s="6" t="s">
+      <c r="N27" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="P27" s="9">
+      <c r="P27" s="1">
         <v>26</v>
       </c>
-      <c r="Q27" s="6" t="s">
+      <c r="Q27" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="S27" s="9">
+      <c r="S27" s="1">
         <v>26</v>
       </c>
-      <c r="T27" s="10" t="s">
+      <c r="T27" s="3" t="s">
         <v>332</v>
       </c>
     </row>
@@ -2768,45 +2731,44 @@
       <c r="A28" s="1">
         <v>27</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="6" t="s">
         <v>27</v>
       </c>
       <c r="C28" s="2"/>
-      <c r="D28" s="9">
+      <c r="D28" s="1">
         <v>27</v>
       </c>
-      <c r="E28" s="6" t="s">
+      <c r="E28" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="F28" s="8"/>
-      <c r="G28" s="9">
+      <c r="G28" s="1">
         <v>27</v>
       </c>
-      <c r="H28" s="10" t="s">
+      <c r="H28" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="J28" s="9">
+      <c r="J28" s="1">
         <v>27</v>
       </c>
-      <c r="K28" s="6" t="s">
+      <c r="K28" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="M28" s="9">
+      <c r="M28" s="1">
         <v>27</v>
       </c>
-      <c r="N28" s="6" t="s">
+      <c r="N28" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="P28" s="9">
+      <c r="P28" s="1">
         <v>27</v>
       </c>
-      <c r="Q28" s="6" t="s">
+      <c r="Q28" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="S28" s="9">
+      <c r="S28" s="1">
         <v>27</v>
       </c>
-      <c r="T28" s="10" t="s">
+      <c r="T28" s="3" t="s">
         <v>333</v>
       </c>
     </row>
@@ -2814,45 +2776,44 @@
       <c r="A29" s="1">
         <v>28</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="6" t="s">
         <v>28</v>
       </c>
       <c r="C29" s="2"/>
-      <c r="D29" s="9">
+      <c r="D29" s="1">
         <v>28</v>
       </c>
-      <c r="E29" s="6" t="s">
+      <c r="E29" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="F29" s="8"/>
-      <c r="G29" s="9">
+      <c r="G29" s="1">
         <v>28</v>
       </c>
-      <c r="H29" s="10" t="s">
+      <c r="H29" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="J29" s="9">
+      <c r="J29" s="1">
         <v>28</v>
       </c>
-      <c r="K29" s="6" t="s">
+      <c r="K29" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="M29" s="9">
+      <c r="M29" s="1">
         <v>28</v>
       </c>
-      <c r="N29" s="6" t="s">
+      <c r="N29" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="P29" s="9">
+      <c r="P29" s="1">
         <v>28</v>
       </c>
-      <c r="Q29" s="6" t="s">
+      <c r="Q29" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="S29" s="9">
+      <c r="S29" s="1">
         <v>28</v>
       </c>
-      <c r="T29" s="10" t="s">
+      <c r="T29" s="3" t="s">
         <v>334</v>
       </c>
     </row>
@@ -2860,45 +2821,44 @@
       <c r="A30" s="1">
         <v>29</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="6" t="s">
         <v>29</v>
       </c>
       <c r="C30" s="2"/>
-      <c r="D30" s="9">
+      <c r="D30" s="1">
         <v>29</v>
       </c>
-      <c r="E30" s="6" t="s">
+      <c r="E30" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="F30" s="8"/>
-      <c r="G30" s="9">
+      <c r="G30" s="1">
         <v>29</v>
       </c>
-      <c r="H30" s="10" t="s">
+      <c r="H30" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="J30" s="9">
+      <c r="J30" s="1">
         <v>29</v>
       </c>
-      <c r="K30" s="6" t="s">
+      <c r="K30" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="M30" s="9">
+      <c r="M30" s="1">
         <v>29</v>
       </c>
-      <c r="N30" s="6" t="s">
+      <c r="N30" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="P30" s="9">
+      <c r="P30" s="1">
         <v>29</v>
       </c>
-      <c r="Q30" s="6" t="s">
+      <c r="Q30" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="S30" s="9">
+      <c r="S30" s="1">
         <v>29</v>
       </c>
-      <c r="T30" s="10" t="s">
+      <c r="T30" s="3" t="s">
         <v>335</v>
       </c>
     </row>
@@ -2906,45 +2866,44 @@
       <c r="A31" s="1">
         <v>30</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C31" s="2"/>
-      <c r="D31" s="9">
+      <c r="D31" s="1">
         <v>30</v>
       </c>
-      <c r="E31" s="6" t="s">
+      <c r="E31" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="F31" s="8"/>
-      <c r="G31" s="9">
+      <c r="G31" s="1">
         <v>30</v>
       </c>
-      <c r="H31" s="10" t="s">
+      <c r="H31" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="J31" s="9">
+      <c r="J31" s="1">
         <v>30</v>
       </c>
-      <c r="K31" s="6" t="s">
+      <c r="K31" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="M31" s="9">
+      <c r="M31" s="1">
         <v>30</v>
       </c>
-      <c r="N31" s="6" t="s">
+      <c r="N31" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="P31" s="9">
+      <c r="P31" s="1">
         <v>30</v>
       </c>
-      <c r="Q31" s="6" t="s">
+      <c r="Q31" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="S31" s="9">
+      <c r="S31" s="1">
         <v>30</v>
       </c>
-      <c r="T31" s="10" t="s">
+      <c r="T31" s="3" t="s">
         <v>336</v>
       </c>
     </row>
@@ -2952,45 +2911,44 @@
       <c r="A32" s="1">
         <v>31</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B32" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C32" s="2"/>
-      <c r="D32" s="9">
+      <c r="D32" s="1">
         <v>31</v>
       </c>
-      <c r="E32" s="10" t="s">
+      <c r="E32" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="F32" s="8"/>
-      <c r="G32" s="9">
+      <c r="G32" s="1">
         <v>31</v>
       </c>
-      <c r="H32" s="10" t="s">
+      <c r="H32" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="J32" s="9">
+      <c r="J32" s="1">
         <v>31</v>
       </c>
-      <c r="K32" s="6" t="s">
+      <c r="K32" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="M32" s="9">
+      <c r="M32" s="1">
         <v>31</v>
       </c>
-      <c r="N32" s="6" t="s">
+      <c r="N32" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="P32" s="9">
+      <c r="P32" s="1">
         <v>31</v>
       </c>
-      <c r="Q32" s="6" t="s">
+      <c r="Q32" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="S32" s="9">
+      <c r="S32" s="1">
         <v>31</v>
       </c>
-      <c r="T32" s="10" t="s">
+      <c r="T32" s="3" t="s">
         <v>337</v>
       </c>
     </row>
@@ -2998,45 +2956,44 @@
       <c r="A33" s="1">
         <v>32</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B33" s="6" t="s">
         <v>32</v>
       </c>
       <c r="C33" s="2"/>
-      <c r="D33" s="9">
+      <c r="D33" s="1">
         <v>32</v>
       </c>
-      <c r="E33" s="10" t="s">
+      <c r="E33" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="F33" s="8"/>
-      <c r="G33" s="9">
+      <c r="G33" s="1">
         <v>32</v>
       </c>
-      <c r="H33" s="10" t="s">
+      <c r="H33" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="J33" s="9">
+      <c r="J33" s="1">
         <v>32</v>
       </c>
-      <c r="K33" s="6" t="s">
+      <c r="K33" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="M33" s="9">
+      <c r="M33" s="1">
         <v>32</v>
       </c>
-      <c r="N33" s="6" t="s">
+      <c r="N33" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="P33" s="9">
+      <c r="P33" s="1">
         <v>32</v>
       </c>
-      <c r="Q33" s="6" t="s">
+      <c r="Q33" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="S33" s="9">
+      <c r="S33" s="1">
         <v>32</v>
       </c>
-      <c r="T33" s="10" t="s">
+      <c r="T33" s="3" t="s">
         <v>338</v>
       </c>
     </row>
@@ -3044,45 +3001,44 @@
       <c r="A34" s="1">
         <v>33</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B34" s="6" t="s">
         <v>33</v>
       </c>
       <c r="C34" s="2"/>
-      <c r="D34" s="9">
+      <c r="D34" s="1">
         <v>33</v>
       </c>
-      <c r="E34" s="10" t="s">
+      <c r="E34" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="F34" s="8"/>
-      <c r="G34" s="9">
+      <c r="G34" s="1">
         <v>33</v>
       </c>
-      <c r="H34" s="10" t="s">
+      <c r="H34" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="J34" s="9">
+      <c r="J34" s="1">
         <v>33</v>
       </c>
-      <c r="K34" s="6" t="s">
+      <c r="K34" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="M34" s="9">
+      <c r="M34" s="1">
         <v>33</v>
       </c>
-      <c r="N34" s="6" t="s">
+      <c r="N34" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="P34" s="9">
+      <c r="P34" s="1">
         <v>33</v>
       </c>
-      <c r="Q34" s="6" t="s">
+      <c r="Q34" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="S34" s="9">
+      <c r="S34" s="1">
         <v>33</v>
       </c>
-      <c r="T34" s="10" t="s">
+      <c r="T34" s="3" t="s">
         <v>339</v>
       </c>
     </row>
@@ -3090,45 +3046,44 @@
       <c r="A35" s="1">
         <v>34</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B35" s="6" t="s">
         <v>34</v>
       </c>
       <c r="C35" s="2"/>
-      <c r="D35" s="9">
+      <c r="D35" s="1">
         <v>34</v>
       </c>
-      <c r="E35" s="10" t="s">
+      <c r="E35" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F35" s="8"/>
-      <c r="G35" s="9">
+      <c r="G35" s="1">
         <v>34</v>
       </c>
-      <c r="H35" s="10" t="s">
+      <c r="H35" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="J35" s="9">
+      <c r="J35" s="1">
         <v>34</v>
       </c>
-      <c r="K35" s="6" t="s">
+      <c r="K35" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="M35" s="9">
+      <c r="M35" s="1">
         <v>34</v>
       </c>
-      <c r="N35" s="6" t="s">
+      <c r="N35" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="P35" s="9">
+      <c r="P35" s="1">
         <v>34</v>
       </c>
-      <c r="Q35" s="6" t="s">
+      <c r="Q35" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="S35" s="9">
+      <c r="S35" s="1">
         <v>34</v>
       </c>
-      <c r="T35" s="10" t="s">
+      <c r="T35" s="3" t="s">
         <v>340</v>
       </c>
     </row>
@@ -3136,45 +3091,44 @@
       <c r="A36" s="1">
         <v>35</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B36" s="6" t="s">
         <v>35</v>
       </c>
       <c r="C36" s="2"/>
-      <c r="D36" s="9">
+      <c r="D36" s="1">
         <v>35</v>
       </c>
-      <c r="E36" s="10" t="s">
+      <c r="E36" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="F36" s="8"/>
-      <c r="G36" s="9">
+      <c r="G36" s="1">
         <v>35</v>
       </c>
-      <c r="H36" s="10" t="s">
+      <c r="H36" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="J36" s="9">
+      <c r="J36" s="1">
         <v>35</v>
       </c>
-      <c r="K36" s="6" t="s">
+      <c r="K36" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="M36" s="9">
+      <c r="M36" s="1">
         <v>35</v>
       </c>
-      <c r="N36" s="6" t="s">
+      <c r="N36" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="P36" s="9">
+      <c r="P36" s="1">
         <v>35</v>
       </c>
-      <c r="Q36" s="6" t="s">
+      <c r="Q36" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="S36" s="9">
+      <c r="S36" s="1">
         <v>35</v>
       </c>
-      <c r="T36" s="10" t="s">
+      <c r="T36" s="3" t="s">
         <v>341</v>
       </c>
     </row>
@@ -3182,45 +3136,44 @@
       <c r="A37" s="1">
         <v>36</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B37" s="6" t="s">
         <v>36</v>
       </c>
       <c r="C37" s="2"/>
-      <c r="D37" s="9">
+      <c r="D37" s="1">
         <v>36</v>
       </c>
-      <c r="E37" s="10" t="s">
+      <c r="E37" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="F37" s="8"/>
-      <c r="G37" s="9">
+      <c r="G37" s="1">
         <v>36</v>
       </c>
-      <c r="H37" s="10" t="s">
+      <c r="H37" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="J37" s="9">
+      <c r="J37" s="1">
         <v>36</v>
       </c>
-      <c r="K37" s="6" t="s">
+      <c r="K37" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="M37" s="9">
+      <c r="M37" s="1">
         <v>36</v>
       </c>
-      <c r="N37" s="6" t="s">
+      <c r="N37" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="P37" s="9">
+      <c r="P37" s="1">
         <v>36</v>
       </c>
-      <c r="Q37" s="6" t="s">
+      <c r="Q37" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="S37" s="9">
+      <c r="S37" s="1">
         <v>36</v>
       </c>
-      <c r="T37" s="10" t="s">
+      <c r="T37" s="3" t="s">
         <v>342</v>
       </c>
     </row>
@@ -3228,45 +3181,44 @@
       <c r="A38" s="1">
         <v>37</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B38" s="6" t="s">
         <v>37</v>
       </c>
       <c r="C38" s="2"/>
-      <c r="D38" s="9">
+      <c r="D38" s="1">
         <v>37</v>
       </c>
-      <c r="E38" s="10" t="s">
+      <c r="E38" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="F38" s="8"/>
-      <c r="G38" s="9">
+      <c r="G38" s="1">
         <v>37</v>
       </c>
-      <c r="H38" s="10" t="s">
+      <c r="H38" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="J38" s="9">
+      <c r="J38" s="1">
         <v>37</v>
       </c>
-      <c r="K38" s="6" t="s">
+      <c r="K38" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="M38" s="9">
+      <c r="M38" s="1">
         <v>37</v>
       </c>
-      <c r="N38" s="6" t="s">
+      <c r="N38" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="P38" s="9">
+      <c r="P38" s="1">
         <v>37</v>
       </c>
-      <c r="Q38" s="6" t="s">
+      <c r="Q38" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="S38" s="9">
+      <c r="S38" s="1">
         <v>37</v>
       </c>
-      <c r="T38" s="10" t="s">
+      <c r="T38" s="3" t="s">
         <v>343</v>
       </c>
     </row>
@@ -3274,45 +3226,44 @@
       <c r="A39" s="1">
         <v>38</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B39" s="6" t="s">
         <v>38</v>
       </c>
       <c r="C39" s="2"/>
-      <c r="D39" s="9">
+      <c r="D39" s="1">
         <v>38</v>
       </c>
-      <c r="E39" s="10" t="s">
+      <c r="E39" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="F39" s="8"/>
-      <c r="G39" s="9">
+      <c r="G39" s="1">
         <v>38</v>
       </c>
-      <c r="H39" s="10" t="s">
+      <c r="H39" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="J39" s="9">
+      <c r="J39" s="1">
         <v>38</v>
       </c>
-      <c r="K39" s="6" t="s">
+      <c r="K39" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="M39" s="9">
+      <c r="M39" s="1">
         <v>38</v>
       </c>
-      <c r="N39" s="6" t="s">
+      <c r="N39" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="P39" s="9">
+      <c r="P39" s="1">
         <v>38</v>
       </c>
-      <c r="Q39" s="6" t="s">
+      <c r="Q39" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="S39" s="9">
+      <c r="S39" s="1">
         <v>38</v>
       </c>
-      <c r="T39" s="10" t="s">
+      <c r="T39" s="3" t="s">
         <v>344</v>
       </c>
     </row>
@@ -3320,45 +3271,44 @@
       <c r="A40" s="1">
         <v>39</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="B40" s="6" t="s">
         <v>39</v>
       </c>
       <c r="C40" s="2"/>
-      <c r="D40" s="9">
+      <c r="D40" s="1">
         <v>39</v>
       </c>
-      <c r="E40" s="10" t="s">
+      <c r="E40" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="F40" s="8"/>
-      <c r="G40" s="9">
+      <c r="G40" s="1">
         <v>39</v>
       </c>
-      <c r="H40" s="10" t="s">
+      <c r="H40" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="J40" s="9">
+      <c r="J40" s="1">
         <v>39</v>
       </c>
-      <c r="K40" s="6" t="s">
+      <c r="K40" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="M40" s="9">
+      <c r="M40" s="1">
         <v>39</v>
       </c>
-      <c r="N40" s="6" t="s">
+      <c r="N40" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="P40" s="9">
+      <c r="P40" s="1">
         <v>39</v>
       </c>
-      <c r="Q40" s="6" t="s">
+      <c r="Q40" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="S40" s="9">
+      <c r="S40" s="1">
         <v>39</v>
       </c>
-      <c r="T40" s="10" t="s">
+      <c r="T40" s="3" t="s">
         <v>345</v>
       </c>
     </row>
@@ -3366,45 +3316,44 @@
       <c r="A41" s="1">
         <v>40</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="B41" s="6" t="s">
         <v>40</v>
       </c>
       <c r="C41" s="2"/>
-      <c r="D41" s="9">
+      <c r="D41" s="1">
         <v>40</v>
       </c>
-      <c r="E41" s="10" t="s">
+      <c r="E41" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="F41" s="8"/>
-      <c r="G41" s="9">
+      <c r="G41" s="1">
         <v>40</v>
       </c>
-      <c r="H41" s="10" t="s">
+      <c r="H41" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="J41" s="9">
+      <c r="J41" s="1">
         <v>40</v>
       </c>
-      <c r="K41" s="6" t="s">
+      <c r="K41" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="M41" s="9">
+      <c r="M41" s="1">
         <v>40</v>
       </c>
-      <c r="N41" s="6" t="s">
+      <c r="N41" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="P41" s="9">
+      <c r="P41" s="1">
         <v>40</v>
       </c>
-      <c r="Q41" s="6" t="s">
+      <c r="Q41" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="S41" s="9">
+      <c r="S41" s="1">
         <v>40</v>
       </c>
-      <c r="T41" s="10" t="s">
+      <c r="T41" s="3" t="s">
         <v>346</v>
       </c>
     </row>
@@ -3416,41 +3365,40 @@
         <v>41</v>
       </c>
       <c r="C42" s="2"/>
-      <c r="D42" s="9">
+      <c r="D42" s="1">
         <v>41</v>
       </c>
-      <c r="E42" s="10" t="s">
+      <c r="E42" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="F42" s="8"/>
-      <c r="G42" s="9">
+      <c r="G42" s="1">
         <v>41</v>
       </c>
-      <c r="H42" s="10" t="s">
+      <c r="H42" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="J42" s="9">
+      <c r="J42" s="1">
         <v>41</v>
       </c>
-      <c r="K42" s="6" t="s">
+      <c r="K42" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="M42" s="9">
+      <c r="M42" s="1">
         <v>41</v>
       </c>
-      <c r="N42" s="6" t="s">
+      <c r="N42" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="P42" s="9">
+      <c r="P42" s="1">
         <v>41</v>
       </c>
-      <c r="Q42" s="6" t="s">
+      <c r="Q42" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="S42" s="9">
+      <c r="S42" s="1">
         <v>41</v>
       </c>
-      <c r="T42" s="10" t="s">
+      <c r="T42" s="3" t="s">
         <v>347</v>
       </c>
     </row>
@@ -3462,41 +3410,40 @@
         <v>42</v>
       </c>
       <c r="C43" s="2"/>
-      <c r="D43" s="9">
+      <c r="D43" s="1">
         <v>42</v>
       </c>
-      <c r="E43" s="10" t="s">
+      <c r="E43" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="F43" s="8"/>
-      <c r="G43" s="9">
+      <c r="G43" s="1">
         <v>42</v>
       </c>
-      <c r="H43" s="10" t="s">
+      <c r="H43" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="J43" s="9">
+      <c r="J43" s="1">
         <v>42</v>
       </c>
-      <c r="K43" s="6" t="s">
+      <c r="K43" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="M43" s="9">
+      <c r="M43" s="1">
         <v>42</v>
       </c>
-      <c r="N43" s="6" t="s">
+      <c r="N43" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="P43" s="9">
+      <c r="P43" s="1">
         <v>42</v>
       </c>
-      <c r="Q43" s="6" t="s">
+      <c r="Q43" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="S43" s="9">
+      <c r="S43" s="1">
         <v>42</v>
       </c>
-      <c r="T43" s="10" t="s">
+      <c r="T43" s="3" t="s">
         <v>348</v>
       </c>
     </row>
@@ -3508,41 +3455,40 @@
         <v>43</v>
       </c>
       <c r="C44" s="2"/>
-      <c r="D44" s="9">
+      <c r="D44" s="1">
         <v>43</v>
       </c>
-      <c r="E44" s="10" t="s">
+      <c r="E44" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="F44" s="8"/>
-      <c r="G44" s="9">
+      <c r="G44" s="1">
         <v>43</v>
       </c>
-      <c r="H44" s="10" t="s">
+      <c r="H44" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="J44" s="9">
+      <c r="J44" s="1">
         <v>43</v>
       </c>
-      <c r="K44" s="6" t="s">
+      <c r="K44" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="M44" s="9">
+      <c r="M44" s="1">
         <v>43</v>
       </c>
-      <c r="N44" s="6" t="s">
+      <c r="N44" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="P44" s="9">
+      <c r="P44" s="1">
         <v>43</v>
       </c>
-      <c r="Q44" s="6" t="s">
+      <c r="Q44" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="S44" s="9">
+      <c r="S44" s="1">
         <v>43</v>
       </c>
-      <c r="T44" s="10" t="s">
+      <c r="T44" s="3" t="s">
         <v>349</v>
       </c>
     </row>
@@ -3554,41 +3500,40 @@
         <v>44</v>
       </c>
       <c r="C45" s="2"/>
-      <c r="D45" s="9">
+      <c r="D45" s="1">
         <v>44</v>
       </c>
-      <c r="E45" s="10" t="s">
+      <c r="E45" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="F45" s="8"/>
-      <c r="G45" s="9">
+      <c r="G45" s="1">
         <v>44</v>
       </c>
-      <c r="H45" s="10" t="s">
+      <c r="H45" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="J45" s="9">
+      <c r="J45" s="1">
         <v>44</v>
       </c>
-      <c r="K45" s="6" t="s">
+      <c r="K45" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="M45" s="9">
+      <c r="M45" s="1">
         <v>44</v>
       </c>
-      <c r="N45" s="6" t="s">
+      <c r="N45" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="P45" s="9">
+      <c r="P45" s="1">
         <v>44</v>
       </c>
-      <c r="Q45" s="6" t="s">
+      <c r="Q45" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="S45" s="9">
+      <c r="S45" s="1">
         <v>44</v>
       </c>
-      <c r="T45" s="10" t="s">
+      <c r="T45" s="3" t="s">
         <v>350</v>
       </c>
     </row>
@@ -3600,41 +3545,40 @@
         <v>45</v>
       </c>
       <c r="C46" s="2"/>
-      <c r="D46" s="9">
+      <c r="D46" s="1">
         <v>45</v>
       </c>
-      <c r="E46" s="10" t="s">
+      <c r="E46" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="F46" s="8"/>
-      <c r="G46" s="9">
+      <c r="G46" s="1">
         <v>45</v>
       </c>
-      <c r="H46" s="10" t="s">
+      <c r="H46" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="J46" s="9">
+      <c r="J46" s="1">
         <v>45</v>
       </c>
-      <c r="K46" s="6" t="s">
+      <c r="K46" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="M46" s="9">
+      <c r="M46" s="1">
         <v>45</v>
       </c>
-      <c r="N46" s="6" t="s">
+      <c r="N46" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="P46" s="9">
+      <c r="P46" s="1">
         <v>45</v>
       </c>
-      <c r="Q46" s="6" t="s">
+      <c r="Q46" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="S46" s="9">
+      <c r="S46" s="1">
         <v>45</v>
       </c>
-      <c r="T46" s="10" t="s">
+      <c r="T46" s="3" t="s">
         <v>351</v>
       </c>
     </row>
@@ -3646,41 +3590,40 @@
         <v>46</v>
       </c>
       <c r="C47" s="2"/>
-      <c r="D47" s="9">
+      <c r="D47" s="1">
         <v>46</v>
       </c>
-      <c r="E47" s="6" t="s">
+      <c r="E47" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="F47" s="8"/>
-      <c r="G47" s="9">
+      <c r="G47" s="1">
         <v>46</v>
       </c>
-      <c r="H47" s="10" t="s">
+      <c r="H47" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="J47" s="9">
+      <c r="J47" s="1">
         <v>46</v>
       </c>
-      <c r="K47" s="6" t="s">
+      <c r="K47" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="M47" s="9">
+      <c r="M47" s="1">
         <v>46</v>
       </c>
-      <c r="N47" s="6" t="s">
+      <c r="N47" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="P47" s="9">
+      <c r="P47" s="1">
         <v>46</v>
       </c>
-      <c r="Q47" s="6" t="s">
+      <c r="Q47" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="S47" s="9">
+      <c r="S47" s="1">
         <v>46</v>
       </c>
-      <c r="T47" s="10" t="s">
+      <c r="T47" s="3" t="s">
         <v>352</v>
       </c>
     </row>
@@ -3692,41 +3635,40 @@
         <v>47</v>
       </c>
       <c r="C48" s="2"/>
-      <c r="D48" s="9">
+      <c r="D48" s="1">
         <v>47</v>
       </c>
-      <c r="E48" s="6" t="s">
+      <c r="E48" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="F48" s="8"/>
-      <c r="G48" s="9">
+      <c r="G48" s="1">
         <v>47</v>
       </c>
-      <c r="H48" s="10" t="s">
+      <c r="H48" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="J48" s="9">
+      <c r="J48" s="1">
         <v>47</v>
       </c>
-      <c r="K48" s="6" t="s">
+      <c r="K48" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="M48" s="9">
+      <c r="M48" s="1">
         <v>47</v>
       </c>
-      <c r="N48" s="6" t="s">
+      <c r="N48" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="P48" s="9">
+      <c r="P48" s="1">
         <v>47</v>
       </c>
-      <c r="Q48" s="6" t="s">
+      <c r="Q48" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="S48" s="9">
+      <c r="S48" s="1">
         <v>47</v>
       </c>
-      <c r="T48" s="10" t="s">
+      <c r="T48" s="3" t="s">
         <v>353</v>
       </c>
     </row>
@@ -3738,41 +3680,40 @@
         <v>48</v>
       </c>
       <c r="C49" s="2"/>
-      <c r="D49" s="9">
+      <c r="D49" s="1">
         <v>48</v>
       </c>
-      <c r="E49" s="6" t="s">
+      <c r="E49" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="F49" s="8"/>
-      <c r="G49" s="9">
+      <c r="G49" s="1">
         <v>48</v>
       </c>
-      <c r="H49" s="10" t="s">
+      <c r="H49" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="J49" s="9">
+      <c r="J49" s="1">
         <v>48</v>
       </c>
-      <c r="K49" s="6" t="s">
+      <c r="K49" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="M49" s="9">
+      <c r="M49" s="1">
         <v>48</v>
       </c>
-      <c r="N49" s="6" t="s">
+      <c r="N49" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="P49" s="9">
+      <c r="P49" s="1">
         <v>48</v>
       </c>
-      <c r="Q49" s="6" t="s">
+      <c r="Q49" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="S49" s="9">
+      <c r="S49" s="1">
         <v>48</v>
       </c>
-      <c r="T49" s="10" t="s">
+      <c r="T49" s="3" t="s">
         <v>354</v>
       </c>
     </row>
@@ -3784,41 +3725,40 @@
         <v>49</v>
       </c>
       <c r="C50" s="2"/>
-      <c r="D50" s="9">
+      <c r="D50" s="1">
         <v>49</v>
       </c>
-      <c r="E50" s="6" t="s">
+      <c r="E50" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="F50" s="8"/>
-      <c r="G50" s="9">
+      <c r="G50" s="1">
         <v>49</v>
       </c>
-      <c r="H50" s="10" t="s">
+      <c r="H50" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="J50" s="9">
+      <c r="J50" s="1">
         <v>49</v>
       </c>
-      <c r="K50" s="6" t="s">
+      <c r="K50" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="M50" s="9">
+      <c r="M50" s="1">
         <v>49</v>
       </c>
-      <c r="N50" s="6" t="s">
+      <c r="N50" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="P50" s="9">
+      <c r="P50" s="1">
         <v>49</v>
       </c>
-      <c r="Q50" s="6" t="s">
+      <c r="Q50" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="S50" s="9">
+      <c r="S50" s="1">
         <v>49</v>
       </c>
-      <c r="T50" s="10" t="s">
+      <c r="T50" s="3" t="s">
         <v>355</v>
       </c>
     </row>
@@ -3830,41 +3770,40 @@
         <v>50</v>
       </c>
       <c r="C51" s="2"/>
-      <c r="D51" s="9">
+      <c r="D51" s="1">
         <v>50</v>
       </c>
-      <c r="E51" s="6" t="s">
+      <c r="E51" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="F51" s="8"/>
-      <c r="G51" s="9">
+      <c r="G51" s="1">
         <v>50</v>
       </c>
-      <c r="H51" s="10" t="s">
+      <c r="H51" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="J51" s="9">
+      <c r="J51" s="1">
         <v>50</v>
       </c>
-      <c r="K51" s="6" t="s">
+      <c r="K51" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="M51" s="9">
+      <c r="M51" s="1">
         <v>50</v>
       </c>
-      <c r="N51" s="6" t="s">
+      <c r="N51" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="P51" s="9">
+      <c r="P51" s="1">
         <v>50</v>
       </c>
-      <c r="Q51" s="6" t="s">
+      <c r="Q51" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="S51" s="9">
+      <c r="S51" s="1">
         <v>50</v>
       </c>
-      <c r="T51" s="10" t="s">
+      <c r="T51" s="3" t="s">
         <v>356</v>
       </c>
     </row>
